--- a/site/PA07_Campaign_Finance.xlsx
+++ b/site/PA07_Campaign_Finance.xlsx
@@ -43,7 +43,7 @@
     <numFmt numFmtId="176" formatCode="+0.0000;-0.0000"/>
     <numFmt numFmtId="177" formatCode="&quot;p = &quot;0.000"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,12 +87,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -159,17 +153,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAF3EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -204,17 +198,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -225,108 +219,106 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="175" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -3610,7 +3602,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17T21:20:04Z</t>
+          <t>2026-09-17T21:38:55Z</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -4349,11 +4341,11 @@
       <c r="R18" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="S18" s="75">
+      <c r="S18" s="73">
         <f>'Money vs Results'!G6</f>
         <v/>
       </c>
-      <c r="T18" s="75">
+      <c r="T18" s="73">
         <f>'Money vs Results'!H6</f>
         <v/>
       </c>
@@ -4362,11 +4354,11 @@
       <c r="R19" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="S19" s="75">
+      <c r="S19" s="73">
         <f>'Money vs Results'!G7</f>
         <v/>
       </c>
-      <c r="T19" s="75">
+      <c r="T19" s="73">
         <f>'Money vs Results'!H7</f>
         <v/>
       </c>
@@ -4375,11 +4367,11 @@
       <c r="R20" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="S20" s="75">
+      <c r="S20" s="73">
         <f>'Money vs Results'!G8</f>
         <v/>
       </c>
-      <c r="T20" s="75">
+      <c r="T20" s="73">
         <f>'Money vs Results'!H8</f>
         <v/>
       </c>
@@ -4388,11 +4380,11 @@
       <c r="R21" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="S21" s="75">
+      <c r="S21" s="73">
         <f>'Money vs Results'!G9</f>
         <v/>
       </c>
-      <c r="T21" s="75">
+      <c r="T21" s="73">
         <f>'Money vs Results'!H9</f>
         <v/>
       </c>
@@ -4425,11 +4417,11 @@
       <c r="R25" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="S25" s="75">
+      <c r="S25" s="73">
         <f>'Money vs Results'!D6</f>
         <v/>
       </c>
-      <c r="T25" s="75">
+      <c r="T25" s="73">
         <f>'Money vs Results'!H6</f>
         <v/>
       </c>
@@ -4438,11 +4430,11 @@
       <c r="R26" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="S26" s="75">
+      <c r="S26" s="73">
         <f>'Money vs Results'!D7</f>
         <v/>
       </c>
-      <c r="T26" s="75">
+      <c r="T26" s="73">
         <f>'Money vs Results'!H7</f>
         <v/>
       </c>
@@ -4451,11 +4443,11 @@
       <c r="R27" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="S27" s="75">
+      <c r="S27" s="73">
         <f>'Money vs Results'!D8</f>
         <v/>
       </c>
-      <c r="T27" s="75">
+      <c r="T27" s="73">
         <f>'Money vs Results'!H8</f>
         <v/>
       </c>
@@ -4464,11 +4456,11 @@
       <c r="R28" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="S28" s="75">
+      <c r="S28" s="73">
         <f>'Money vs Results'!D9</f>
         <v/>
       </c>
-      <c r="T28" s="75">
+      <c r="T28" s="73">
         <f>'Money vs Results'!H9</f>
         <v/>
       </c>
@@ -4501,11 +4493,11 @@
       <c r="R32" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="S32" s="75">
+      <c r="S32" s="73">
         <f>'Money vs Results'!H6</f>
         <v/>
       </c>
-      <c r="T32" s="76" t="n">
+      <c r="T32" s="74" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4513,11 +4505,11 @@
       <c r="R33" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="S33" s="75">
+      <c r="S33" s="73">
         <f>'Money vs Results'!H7</f>
         <v/>
       </c>
-      <c r="T33" s="76" t="n">
+      <c r="T33" s="74" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4525,11 +4517,11 @@
       <c r="R34" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="S34" s="75">
+      <c r="S34" s="73">
         <f>'Money vs Results'!H8</f>
         <v/>
       </c>
-      <c r="T34" s="76" t="n">
+      <c r="T34" s="74" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4537,11 +4529,11 @@
       <c r="R35" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="S35" s="75">
+      <c r="S35" s="73">
         <f>'Money vs Results'!H9</f>
         <v/>
       </c>
-      <c r="T35" s="76" t="n">
+      <c r="T35" s="74" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4646,7 +4638,7 @@
           <t>2018 Wild (D)</t>
         </is>
       </c>
-      <c r="S46" s="77">
+      <c r="S46" s="75">
         <f>History!R6</f>
         <v/>
       </c>
@@ -4657,7 +4649,7 @@
           <t>2018 Nothstein (R)</t>
         </is>
       </c>
-      <c r="S47" s="77">
+      <c r="S47" s="75">
         <f>History!R7</f>
         <v/>
       </c>
@@ -4668,7 +4660,7 @@
           <t>2020 Wild (D)</t>
         </is>
       </c>
-      <c r="S48" s="77">
+      <c r="S48" s="75">
         <f>History!R8</f>
         <v/>
       </c>
@@ -4679,7 +4671,7 @@
           <t>2020 Scheller (R)</t>
         </is>
       </c>
-      <c r="S49" s="77">
+      <c r="S49" s="75">
         <f>History!R9</f>
         <v/>
       </c>
@@ -4690,7 +4682,7 @@
           <t>2022 Wild (D)</t>
         </is>
       </c>
-      <c r="S50" s="77">
+      <c r="S50" s="75">
         <f>History!R10</f>
         <v/>
       </c>
@@ -4701,7 +4693,7 @@
           <t>2022 Scheller (R)</t>
         </is>
       </c>
-      <c r="S51" s="77">
+      <c r="S51" s="75">
         <f>History!R11</f>
         <v/>
       </c>
@@ -4712,7 +4704,7 @@
           <t>2024 Wild (D)</t>
         </is>
       </c>
-      <c r="S52" s="77">
+      <c r="S52" s="75">
         <f>History!R12</f>
         <v/>
       </c>
@@ -4723,7 +4715,7 @@
           <t>2024 Mackenzie (R)</t>
         </is>
       </c>
-      <c r="S53" s="77">
+      <c r="S53" s="75">
         <f>History!R13</f>
         <v/>
       </c>
@@ -4836,7 +4828,7 @@
         <f>SUMIFS(History!$G$6:$G$13,History!$A$6:$A$13,$A6,History!$E$6:$E$13,"REP")</f>
         <v/>
       </c>
-      <c r="D6" s="67">
+      <c r="D6" s="65">
         <f>IF(B6+C6=0,"",B6/(B6+C6))</f>
         <v/>
       </c>
@@ -4848,7 +4840,7 @@
         <f>SUMIFS(History!$N$6:$N$13,History!$A$6:$A$13,$A6,History!$E$6:$E$13,"REP")</f>
         <v/>
       </c>
-      <c r="G6" s="67">
+      <c r="G6" s="65">
         <f>IF(E6+F6=0,"",E6/(E6+F6))</f>
         <v/>
       </c>
@@ -4869,7 +4861,7 @@
         <f>SUMIFS(History!$G$6:$G$13,History!$A$6:$A$13,$A7,History!$E$6:$E$13,"REP")</f>
         <v/>
       </c>
-      <c r="D7" s="67">
+      <c r="D7" s="65">
         <f>IF(B7+C7=0,"",B7/(B7+C7))</f>
         <v/>
       </c>
@@ -4881,7 +4873,7 @@
         <f>SUMIFS(History!$N$6:$N$13,History!$A$6:$A$13,$A7,History!$E$6:$E$13,"REP")</f>
         <v/>
       </c>
-      <c r="G7" s="67">
+      <c r="G7" s="65">
         <f>IF(E7+F7=0,"",E7/(E7+F7))</f>
         <v/>
       </c>
@@ -4902,7 +4894,7 @@
         <f>SUMIFS(History!$G$6:$G$13,History!$A$6:$A$13,$A8,History!$E$6:$E$13,"REP")</f>
         <v/>
       </c>
-      <c r="D8" s="67">
+      <c r="D8" s="65">
         <f>IF(B8+C8=0,"",B8/(B8+C8))</f>
         <v/>
       </c>
@@ -4914,7 +4906,7 @@
         <f>SUMIFS(History!$N$6:$N$13,History!$A$6:$A$13,$A8,History!$E$6:$E$13,"REP")</f>
         <v/>
       </c>
-      <c r="G8" s="67">
+      <c r="G8" s="65">
         <f>IF(E8+F8=0,"",E8/(E8+F8))</f>
         <v/>
       </c>
@@ -4935,7 +4927,7 @@
         <f>SUMIFS(History!$G$6:$G$13,History!$A$6:$A$13,$A9,History!$E$6:$E$13,"REP")</f>
         <v/>
       </c>
-      <c r="D9" s="67">
+      <c r="D9" s="65">
         <f>IF(B9+C9=0,"",B9/(B9+C9))</f>
         <v/>
       </c>
@@ -4947,7 +4939,7 @@
         <f>SUMIFS(History!$N$6:$N$13,History!$A$6:$A$13,$A9,History!$E$6:$E$13,"REP")</f>
         <v/>
       </c>
-      <c r="G9" s="67">
+      <c r="G9" s="65">
         <f>IF(E9+F9=0,"",E9/(E9+F9))</f>
         <v/>
       </c>
@@ -4998,11 +4990,11 @@
           <t>Observations (n)</t>
         </is>
       </c>
-      <c r="B13" s="78">
+      <c r="B13" s="76">
         <f>COUNT(H6:H9)</f>
         <v/>
       </c>
-      <c r="C13" s="78">
+      <c r="C13" s="76">
         <f>COUNT(H6:H9)</f>
         <v/>
       </c>
@@ -5013,11 +5005,11 @@
           <t>Pearson correlation r</t>
         </is>
       </c>
-      <c r="B14" s="79">
+      <c r="B14" s="77">
         <f>IFERROR(CORREL(D6:D9,H6:H9),"")</f>
         <v/>
       </c>
-      <c r="C14" s="79">
+      <c r="C14" s="77">
         <f>IFERROR(CORREL(G6:G9,H6:H9),"")</f>
         <v/>
       </c>
@@ -5028,11 +5020,11 @@
           <t>R squared (variance explained)</t>
         </is>
       </c>
-      <c r="B15" s="80">
+      <c r="B15" s="78">
         <f>IFERROR(RSQ(H6:H9,D6:D9),"")</f>
         <v/>
       </c>
-      <c r="C15" s="80">
+      <c r="C15" s="78">
         <f>IFERROR(RSQ(H6:H9,G6:G9),"")</f>
         <v/>
       </c>
@@ -5043,11 +5035,11 @@
           <t>Slope (change in vote share per 1.0 of money share)</t>
         </is>
       </c>
-      <c r="B16" s="79">
+      <c r="B16" s="77">
         <f>IFERROR(SLOPE(H6:H9,D6:D9),"")</f>
         <v/>
       </c>
-      <c r="C16" s="79">
+      <c r="C16" s="77">
         <f>IFERROR(SLOPE(H6:H9,G6:G9),"")</f>
         <v/>
       </c>
@@ -5058,11 +5050,11 @@
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B17" s="80">
+      <c r="B17" s="78">
         <f>IFERROR(INTERCEPT(H6:H9,D6:D9),"")</f>
         <v/>
       </c>
-      <c r="C17" s="80">
+      <c r="C17" s="78">
         <f>IFERROR(INTERCEPT(H6:H9,G6:G9),"")</f>
         <v/>
       </c>
@@ -5073,11 +5065,11 @@
           <t>Standard error of the slope</t>
         </is>
       </c>
-      <c r="B18" s="81">
+      <c r="B18" s="79">
         <f>IFERROR(STEYX(H6:H9,D6:D9)/SQRT(DEVSQ(D6:D9)),"")</f>
         <v/>
       </c>
-      <c r="C18" s="81">
+      <c r="C18" s="79">
         <f>IFERROR(STEYX(H6:H9,G6:G9)/SQRT(DEVSQ(G6:G9)),"")</f>
         <v/>
       </c>
@@ -5088,11 +5080,11 @@
           <t>t-statistic for the slope</t>
         </is>
       </c>
-      <c r="B19" s="79">
+      <c r="B19" s="77">
         <f>IF(AND(ISNUMBER(B16),ISNUMBER(B18),B18&lt;&gt;0),B16/B18,"")</f>
         <v/>
       </c>
-      <c r="C19" s="79">
+      <c r="C19" s="77">
         <f>IF(AND(ISNUMBER(C16),ISNUMBER(C18),C18&lt;&gt;0),C16/C18,"")</f>
         <v/>
       </c>
@@ -5103,11 +5095,11 @@
           <t>p-value (two-tailed)</t>
         </is>
       </c>
-      <c r="B20" s="82">
+      <c r="B20" s="80">
         <f>IF(AND(ISNUMBER(B19),B21&gt;0),IFERROR(TDIST(ABS(B19),B21,2),""),"")</f>
         <v/>
       </c>
-      <c r="C20" s="82">
+      <c r="C20" s="80">
         <f>IF(AND(ISNUMBER(C19),C21&gt;0),IFERROR(TDIST(ABS(C19),C21,2),""),"")</f>
         <v/>
       </c>
@@ -5118,11 +5110,11 @@
           <t>Degrees of freedom</t>
         </is>
       </c>
-      <c r="B21" s="78">
+      <c r="B21" s="76">
         <f>IF(ISNUMBER(B13),B13-2,"")</f>
         <v/>
       </c>
-      <c r="C21" s="78">
+      <c r="C21" s="76">
         <f>IF(ISNUMBER(C13),C13-2,"")</f>
         <v/>
       </c>
@@ -5133,11 +5125,11 @@
           <t>Statistically significant at p &lt; 0.05?</t>
         </is>
       </c>
-      <c r="B22" s="83">
+      <c r="B22" s="81">
         <f>IF(ISNUMBER(B20),IF(B20&lt;0.05,"yes","no: cannot reject the null"),"")</f>
         <v/>
       </c>
-      <c r="C22" s="83">
+      <c r="C22" s="81">
         <f>IF(ISNUMBER(C20),IF(C20&lt;0.05,"yes","no: cannot reject the null"),"")</f>
         <v/>
       </c>
@@ -5195,11 +5187,11 @@
         <f>H6</f>
         <v/>
       </c>
-      <c r="C26" s="67">
+      <c r="C26" s="65">
         <f>IF(AND(ISNUMBER($C$17),ISNUMBER($C$16),ISNUMBER(E26)),$C$17+$C$16*E26,"")</f>
         <v/>
       </c>
-      <c r="D26" s="84">
+      <c r="D26" s="82">
         <f>IF(AND(ISNUMBER(B26),ISNUMBER(C26)),B26-C26,"")</f>
         <v/>
       </c>
@@ -5217,11 +5209,11 @@
         <f>H7</f>
         <v/>
       </c>
-      <c r="C27" s="67">
+      <c r="C27" s="65">
         <f>IF(AND(ISNUMBER($C$17),ISNUMBER($C$16),ISNUMBER(E27)),$C$17+$C$16*E27,"")</f>
         <v/>
       </c>
-      <c r="D27" s="84">
+      <c r="D27" s="82">
         <f>IF(AND(ISNUMBER(B27),ISNUMBER(C27)),B27-C27,"")</f>
         <v/>
       </c>
@@ -5239,11 +5231,11 @@
         <f>H8</f>
         <v/>
       </c>
-      <c r="C28" s="67">
+      <c r="C28" s="65">
         <f>IF(AND(ISNUMBER($C$17),ISNUMBER($C$16),ISNUMBER(E28)),$C$17+$C$16*E28,"")</f>
         <v/>
       </c>
-      <c r="D28" s="84">
+      <c r="D28" s="82">
         <f>IF(AND(ISNUMBER(B28),ISNUMBER(C28)),B28-C28,"")</f>
         <v/>
       </c>
@@ -5261,11 +5253,11 @@
         <f>H9</f>
         <v/>
       </c>
-      <c r="C29" s="67">
+      <c r="C29" s="65">
         <f>IF(AND(ISNUMBER($C$17),ISNUMBER($C$16),ISNUMBER(E29)),$C$17+$C$16*E29,"")</f>
         <v/>
       </c>
-      <c r="D29" s="84">
+      <c r="D29" s="82">
         <f>IF(AND(ISNUMBER(B29),ISNUMBER(C29)),B29-C29,"")</f>
         <v/>
       </c>
@@ -5398,42 +5390,42 @@
       </c>
     </row>
     <row r="4" ht="120" customHeight="1">
-      <c r="A4" s="85" t="inlineStr">
-        <is>
-          <t>Current cycle: FEC / OpenFEC API, https://www.fec.gov/data/elections/house/PA/07/2026/, retrieved 2026-09-17T21:20:04Z</t>
+      <c r="A4" s="83" t="inlineStr">
+        <is>
+          <t>Current cycle: FEC / OpenFEC API, https://www.fec.gov/data/elections/house/PA/07/2026/, retrieved 2026-09-17T21:38:55Z</t>
         </is>
       </c>
     </row>
     <row r="5" ht="108" customHeight="1">
-      <c r="A5" s="85" t="inlineStr">
+      <c r="A5" s="83" t="inlineStr">
         <is>
           <t>History, finance: OpenFEC API (finance); certified results from sources/results.json, retrieved 2026-09-17T15:59:59Z</t>
         </is>
       </c>
     </row>
     <row r="6" ht="168" customHeight="1">
-      <c r="A6" s="85" t="inlineStr">
+      <c r="A6" s="83" t="inlineStr">
         <is>
           <t>History, 2018 results: FEC, Federal Elections 2018, '2018 US House Results by State', district '07 - FULL TERM' (https://www.fec.gov/documents/2706/federalelections2018.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="156" customHeight="1">
-      <c r="A7" s="85" t="inlineStr">
+      <c r="A7" s="83" t="inlineStr">
         <is>
           <t>History, 2020 results: FEC, Federal Elections 2020, '13. US House Results by State', district '07' (https://www.fec.gov/documents/4228/federalelections2020.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="156" customHeight="1">
-      <c r="A8" s="85" t="inlineStr">
+      <c r="A8" s="83" t="inlineStr">
         <is>
           <t>History, 2022 results: FEC, Federal Elections 2022, '8. US House Results by State', district '07' (https://www.fec.gov/documents/5676/federalelections2022.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="204" customHeight="1">
-      <c r="A9" s="85" t="inlineStr">
+      <c r="A9" s="83" t="inlineStr">
         <is>
           <t>History, 2024 results: Clerk of the U.S. House, Statistics of the Congressional Election of November 5, 2024, p.61 (Pennsylvania, district 7) (https://clerk.house.gov/member_info/electionInfo/2024/statistics2024.pdf)</t>
         </is>
@@ -6685,11 +6677,11 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$K$6:$K$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$K$6:$K$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))-INDEX('Candidate Totals'!$L$6:$L$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$K$6:$K$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$K$6:$K$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))-INDEX('Candidate Totals'!$L$6:$L$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C6" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$K$6:$K$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$K$6:$K$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))-INDEX('Candidate Totals'!$L$6:$L$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$K$6:$K$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$K$6:$K$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))-INDEX('Candidate Totals'!$L$6:$L$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="D6" s="22">
@@ -6708,11 +6700,11 @@
         </is>
       </c>
       <c r="B7" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$L$6:$L$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$L$6:$L$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$L$6:$L$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$L$6:$L$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C7" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$L$6:$L$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$L$6:$L$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$L$6:$L$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$L$6:$L$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="D7" s="22">
@@ -6731,11 +6723,11 @@
         </is>
       </c>
       <c r="B8" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$M$6:$M$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$M$6:$M$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$M$6:$M$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$M$6:$M$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C8" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$M$6:$M$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$M$6:$M$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$M$6:$M$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$M$6:$M$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="D8" s="22">
@@ -6754,11 +6746,11 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$N$6:$N$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$N$6:$N$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$N$6:$N$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$N$6:$N$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C9" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$N$6:$N$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$N$6:$N$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$N$6:$N$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$N$6:$N$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="D9" s="22">
@@ -6777,11 +6769,11 @@
         </is>
       </c>
       <c r="B10" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$O$6:$O$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$O$6:$O$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$O$6:$O$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$O$6:$O$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C10" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$O$6:$O$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$O$6:$O$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$O$6:$O$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$O$6:$O$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="D10" s="22">
@@ -6800,11 +6792,11 @@
         </is>
       </c>
       <c r="B11" s="12">
-        <f>IFERROR(INDEX('Candidate Totals'!$P$6:$P$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0)),"")</f>
+        <f>IFERROR(INDEX('Candidate Totals'!$P$6:$P$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0)),"")</f>
         <v/>
       </c>
       <c r="C11" s="12">
-        <f>IFERROR(INDEX('Candidate Totals'!$P$6:$P$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0)),"")</f>
+        <f>IFERROR(INDEX('Candidate Totals'!$P$6:$P$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="22">
@@ -6823,11 +6815,11 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$Q$6:$Q$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$Q$6:$Q$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$Q$6:$Q$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$Q$6:$Q$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C12" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$Q$6:$Q$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$Q$6:$Q$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$Q$6:$Q$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$Q$6:$Q$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="D12" s="22">
@@ -6869,11 +6861,11 @@
         </is>
       </c>
       <c r="B14" s="39">
-        <f>IFERROR(B13-INDEX('Candidate Totals'!$G$6:$G$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0)),"")</f>
+        <f>IFERROR(B13-INDEX('Candidate Totals'!$G$6:$G$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0)),"")</f>
         <v/>
       </c>
       <c r="C14" s="39">
-        <f>IFERROR(C13-INDEX('Candidate Totals'!$G$6:$G$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0)),"")</f>
+        <f>IFERROR(C13-INDEX('Candidate Totals'!$G$6:$G$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -6918,11 +6910,11 @@
         </is>
       </c>
       <c r="B18" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$G$6:$G$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$G$6:$G$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$G$6:$G$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$G$6:$G$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C18" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$G$6:$G$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$G$6:$G$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$G$6:$G$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$G$6:$G$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="D18" s="40">
@@ -6937,11 +6929,11 @@
         </is>
       </c>
       <c r="B19" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$O$6:$O$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$O$6:$O$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$O$6:$O$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$O$6:$O$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C19" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$O$6:$O$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$O$6:$O$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$O$6:$O$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$O$6:$O$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="D19" s="40">
@@ -7005,11 +6997,11 @@
         </is>
       </c>
       <c r="B24" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$L$6:$L$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$L$6:$L$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$L$6:$L$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$L$6:$L$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C24" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$L$6:$L$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$L$6:$L$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$L$6:$L$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$L$6:$L$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -7020,11 +7012,11 @@
         </is>
       </c>
       <c r="B25" s="22">
-        <f>IFERROR(B24/(INDEX('Candidate Totals'!$G$6:$G$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(B24/(INDEX('Candidate Totals'!$G$6:$G$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C25" s="22">
-        <f>IFERROR(C24/(INDEX('Candidate Totals'!$G$6:$G$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(C24/(INDEX('Candidate Totals'!$G$6:$G$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -7035,11 +7027,11 @@
         </is>
       </c>
       <c r="B26" s="22">
-        <f>IFERROR(B24/(INDEX('Candidate Totals'!$K$6:$K$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(B24/(INDEX('Candidate Totals'!$K$6:$K$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C26" s="22">
-        <f>IFERROR(C24/(INDEX('Candidate Totals'!$K$6:$K$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(C24/(INDEX('Candidate Totals'!$K$6:$K$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -7084,11 +7076,11 @@
         </is>
       </c>
       <c r="B30" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$G$6:$G$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$G$6:$G$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$G$6:$G$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$G$6:$G$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C30" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$G$6:$G$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$G$6:$G$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$G$6:$G$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$G$6:$G$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="D30" s="40">
@@ -7103,11 +7095,11 @@
         </is>
       </c>
       <c r="B31" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$H$6:$H$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$H$6:$H$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$H$6:$H$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$H$6:$H$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C31" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$H$6:$H$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$H$6:$H$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$H$6:$H$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$H$6:$H$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="D31" s="40">
@@ -7122,11 +7114,11 @@
         </is>
       </c>
       <c r="B32" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$I$6:$I$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$I$6:$I$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$I$6:$I$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$I$6:$I$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="C32" s="12">
-        <f>IFERROR(IF(INDEX('Candidate Totals'!$I$6:$I$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))=0,"",INDEX('Candidate Totals'!$I$6:$I$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0))),"")</f>
+        <f>IFERROR(IF(INDEX('Candidate Totals'!$I$6:$I$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))=0,"",INDEX('Candidate Totals'!$I$6:$I$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0))),"")</f>
         <v/>
       </c>
       <c r="D32" s="40">
@@ -7141,11 +7133,11 @@
         </is>
       </c>
       <c r="B33" s="12">
-        <f>IFERROR(INDEX('Candidate Totals'!$J$6:$J$15,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$15,0)),"")</f>
+        <f>IFERROR(INDEX('Candidate Totals'!$J$6:$J$7,MATCH("Bob Brooks",'Candidate Totals'!$A$6:$A$7,0)),"")</f>
         <v/>
       </c>
       <c r="C33" s="12">
-        <f>IFERROR(INDEX('Candidate Totals'!$J$6:$J$15,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$15,0)),"")</f>
+        <f>IFERROR(INDEX('Candidate Totals'!$J$6:$J$7,MATCH("Ryan Mackenzie",'Candidate Totals'!$A$6:$A$7,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="40">
@@ -7213,7 +7205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7245,14 +7237,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cycle-to-date from each committee's latest periodic FEC report. Coverage through 2026-06-30. Retrieved 2026-09-17T21:20:04Z.</t>
+          <t>Cycle-to-date from each committee's latest periodic FEC report. Coverage through 2026-06-30. Retrieved 2026-09-17T21:38:55Z.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>EVERY DECLARED CANDIDATE</t>
+          <t>THE TWO NOMINEES</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -7492,527 +7484,91 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Ryan Crosswell</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>DEM</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Primary candidate</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G8" s="42" t="n">
-        <v>1872528.13</v>
-      </c>
-      <c r="H8" s="42" t="n">
-        <v>1859323.43</v>
-      </c>
-      <c r="I8" s="42" t="n">
-        <v>13204.7</v>
-      </c>
-      <c r="J8" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="42" t="n">
-        <v>1794415.95</v>
-      </c>
-      <c r="L8" s="42" t="n">
-        <v>407478.81</v>
-      </c>
-      <c r="M8" s="42" t="n">
-        <v>24750</v>
-      </c>
-      <c r="N8" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="42" t="n">
-        <v>49522.52</v>
-      </c>
-      <c r="P8" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="40">
-        <f>IF(ISNUMBER(G8),G8-(K8+M8+N8+O8+P8),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Carol Obando-Derstine</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>DEM</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Primary candidate</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G9" s="42" t="n">
-        <v>593293.48</v>
-      </c>
-      <c r="H9" s="42" t="n">
-        <v>591121.38</v>
-      </c>
-      <c r="I9" s="42" t="n">
-        <v>2172.1</v>
-      </c>
-      <c r="J9" s="42" t="n">
-        <v>35000</v>
-      </c>
-      <c r="K9" s="42" t="n">
-        <v>485269.81</v>
-      </c>
-      <c r="L9" s="42" t="n">
-        <v>131453.58</v>
-      </c>
-      <c r="M9" s="42" t="n">
-        <v>53134.65</v>
-      </c>
-      <c r="N9" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="42" t="n">
-        <v>10889.98</v>
-      </c>
-      <c r="P9" s="42" t="n">
-        <v>9302.34</v>
-      </c>
-      <c r="Q9" s="40">
-        <f>IF(ISNUMBER(G9),G9-(K9+M9+N9+O9+P9),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Lamont McClure</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>DEM</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Primary candidate</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G10" s="42" t="n">
-        <v>515144.34</v>
-      </c>
-      <c r="H10" s="42" t="n">
-        <v>512981.08</v>
-      </c>
-      <c r="I10" s="42" t="n">
-        <v>2163.26</v>
-      </c>
-      <c r="J10" s="42" t="n">
-        <v>200000</v>
-      </c>
-      <c r="K10" s="42" t="n">
-        <v>246039.79</v>
-      </c>
-      <c r="L10" s="42" t="n">
-        <v>54880.62</v>
-      </c>
-      <c r="M10" s="42" t="n">
-        <v>45100</v>
-      </c>
-      <c r="N10" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="42" t="n">
-        <v>24000</v>
-      </c>
-      <c r="Q10" s="40">
-        <f>IF(ISNUMBER(G10),G10-(K10+M10+N10+O10+P10),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Mark Pinsley</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>DEM</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Primary candidate</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G11" s="42" t="n">
-        <v>179911.74</v>
-      </c>
-      <c r="H11" s="42" t="n">
-        <v>125387.79</v>
-      </c>
-      <c r="I11" s="42" t="n">
-        <v>54523.95</v>
-      </c>
-      <c r="J11" s="42" t="n">
-        <v>-1567.67</v>
-      </c>
-      <c r="K11" s="42" t="n">
-        <v>179411.74</v>
-      </c>
-      <c r="L11" s="42" t="n">
-        <v>83715.27</v>
-      </c>
-      <c r="M11" s="42" t="n">
-        <v>500</v>
-      </c>
-      <c r="N11" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="40">
-        <f>IF(ISNUMBER(G11),G11-(K11+M11+N11+O11+P11),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Frank Golden</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Declared</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E12" s="43" t="inlineStr">
-        <is>
-          <t>no report</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="44" t="n"/>
-      <c r="H12" s="44" t="n"/>
-      <c r="I12" s="44" t="n"/>
-      <c r="J12" s="44" t="n"/>
-      <c r="K12" s="44" t="n"/>
-      <c r="L12" s="44" t="n"/>
-      <c r="M12" s="44" t="n"/>
-      <c r="N12" s="44" t="n"/>
-      <c r="O12" s="44" t="n"/>
-      <c r="P12" s="44" t="n"/>
-      <c r="Q12" s="44" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Aiden Alexander Gonzalez</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>DEM</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Primary candidate</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E13" s="43" t="inlineStr">
-        <is>
-          <t>no report</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="44" t="n"/>
-      <c r="I13" s="44" t="n"/>
-      <c r="J13" s="44" t="n"/>
-      <c r="K13" s="44" t="n"/>
-      <c r="L13" s="44" t="n"/>
-      <c r="M13" s="44" t="n"/>
-      <c r="N13" s="44" t="n"/>
-      <c r="O13" s="44" t="n"/>
-      <c r="P13" s="44" t="n"/>
-      <c r="Q13" s="44" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Michael Ramon Granados Jr.</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>Declared</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E14" s="43" t="inlineStr">
-        <is>
-          <t>no report</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="44" t="n"/>
-      <c r="H14" s="44" t="n"/>
-      <c r="I14" s="44" t="n"/>
-      <c r="J14" s="44" t="n"/>
-      <c r="K14" s="44" t="n"/>
-      <c r="L14" s="44" t="n"/>
-      <c r="M14" s="44" t="n"/>
-      <c r="N14" s="44" t="n"/>
-      <c r="O14" s="44" t="n"/>
-      <c r="P14" s="44" t="n"/>
-      <c r="Q14" s="44" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Lewis Shupe</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Declared</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E15" s="43" t="inlineStr">
-        <is>
-          <t>no report</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="44" t="n"/>
-      <c r="H15" s="44" t="n"/>
-      <c r="I15" s="44" t="n"/>
-      <c r="J15" s="44" t="n"/>
-      <c r="K15" s="44" t="n"/>
-      <c r="L15" s="44" t="n"/>
-      <c r="M15" s="44" t="n"/>
-      <c r="N15" s="44" t="n"/>
-      <c r="O15" s="44" t="n"/>
-      <c r="P15" s="44" t="n"/>
-      <c r="Q15" s="44" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL, all candidates who filed</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="17">
-        <f>SUM(G6:G15)</f>
-        <v/>
-      </c>
-      <c r="H16" s="17">
-        <f>SUM(H6:H15)</f>
-        <v/>
-      </c>
-      <c r="I16" s="17">
-        <f>SUM(I6:I15)</f>
-        <v/>
-      </c>
-      <c r="J16" s="17">
-        <f>SUM(J6:J15)</f>
-        <v/>
-      </c>
-      <c r="K16" s="17">
-        <f>SUM(K6:K15)</f>
-        <v/>
-      </c>
-      <c r="L16" s="17">
-        <f>SUM(L6:L15)</f>
-        <v/>
-      </c>
-      <c r="M16" s="17">
-        <f>SUM(M6:M15)</f>
-        <v/>
-      </c>
-      <c r="N16" s="17">
-        <f>SUM(N6:N15)</f>
-        <v/>
-      </c>
-      <c r="O16" s="17">
-        <f>SUM(O6:O15)</f>
-        <v/>
-      </c>
-      <c r="P16" s="17">
-        <f>SUM(P6:P15)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="17">
-        <f>SUM(Q6:Q15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL, both nominees</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="17">
+        <f>SUM(G6:G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
+        <f>SUM(H6:H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="17">
+        <f>SUM(I6:I7)</f>
+        <v/>
+      </c>
+      <c r="J8" s="17">
+        <f>SUM(J6:J7)</f>
+        <v/>
+      </c>
+      <c r="K8" s="17">
+        <f>SUM(K6:K7)</f>
+        <v/>
+      </c>
+      <c r="L8" s="17">
+        <f>SUM(L6:L7)</f>
+        <v/>
+      </c>
+      <c r="M8" s="17">
+        <f>SUM(M6:M7)</f>
+        <v/>
+      </c>
+      <c r="N8" s="17">
+        <f>SUM(N6:N7)</f>
+        <v/>
+      </c>
+      <c r="O8" s="17">
+        <f>SUM(O6:O7)</f>
+        <v/>
+      </c>
+      <c r="P8" s="17">
+        <f>SUM(P6:P7)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="17">
+        <f>SUM(Q6:Q7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>HOW TO READ THIS TABLE</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>Candidates with no periodic report on file have BLANK financial cells, not $0. The FEC reports nothing for them, which is a different claim from 'raised nothing'. SUM() ignores blanks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>'Status' comes from sources/race.json: the two nominees are named there; any other Democrat or Republican who filed is a primary candidate; the rest are declared candidates of other parties.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="32" t="inlineStr">
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>This workbook covers the two general-election nominees named in sources/race.json. The FEC lists other declared and primary candidates for the seat; they stay in sources/fec.json and are not shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>A candidate with no periodic report on file would show BLANK financial cells, not $0. The FEC reports nothing in that case, which is a different claim from 'raised nothing'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>'of which unitemized' is a subset of 'Individual, total'. Adding it to the other source columns double-counts.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="32" t="inlineStr">
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>Blue figures are values from the FEC API. Black figures are formulas.</t>
         </is>
@@ -8020,11 +7576,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A22:Q22"/>
-    <mergeCell ref="A18:Q18"/>
-    <mergeCell ref="A21:Q21"/>
-    <mergeCell ref="A20:Q20"/>
-    <mergeCell ref="A19:Q19"/>
+    <mergeCell ref="A14:Q14"/>
+    <mergeCell ref="A12:Q12"/>
+    <mergeCell ref="A10:Q10"/>
+    <mergeCell ref="A11:Q11"/>
+    <mergeCell ref="A13:Q13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -8125,12 +7681,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C6" s="46" t="inlineStr">
+      <c r="C6" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="45" t="n">
         <v>1781524</v>
       </c>
       <c r="E6" s="14" t="n">
@@ -8157,12 +7713,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C7" s="46" t="inlineStr">
+      <c r="C7" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="45" t="n">
         <v>312371.76</v>
       </c>
       <c r="E7" s="14" t="n">
@@ -8189,12 +7745,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="45" t="n">
         <v>249750</v>
       </c>
       <c r="E8" s="14" t="n">
@@ -8221,12 +7777,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C9" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="45" t="n">
         <v>140300</v>
       </c>
       <c r="E9" s="14" t="n">
@@ -8253,12 +7809,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="45" t="n">
         <v>99625</v>
       </c>
       <c r="E10" s="14" t="n">
@@ -8285,12 +7841,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="45" t="n">
         <v>88321.5</v>
       </c>
       <c r="E11" s="14" t="n">
@@ -8317,12 +7873,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C12" s="46" t="inlineStr">
+      <c r="C12" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="45" t="n">
         <v>30559.95</v>
       </c>
       <c r="E12" s="14" t="n">
@@ -8349,12 +7905,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C13" s="46" t="inlineStr">
+      <c r="C13" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="45" t="n">
         <v>16643.34</v>
       </c>
       <c r="E13" s="14" t="n">
@@ -8381,12 +7937,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="C14" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D14" s="47" t="n">
+      <c r="D14" s="45" t="n">
         <v>9116.67</v>
       </c>
       <c r="E14" s="14" t="n">
@@ -8413,12 +7969,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C15" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="45" t="n">
         <v>8840</v>
       </c>
       <c r="E15" s="14" t="n">
@@ -8445,12 +8001,12 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
       </c>
-      <c r="D16" s="47" t="n">
+      <c r="D16" s="45" t="n">
         <v>6044</v>
       </c>
       <c r="E16" s="14" t="n">
@@ -8477,12 +8033,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C17" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D17" s="47" t="n">
+      <c r="D17" s="45" t="n">
         <v>4941.66</v>
       </c>
       <c r="E17" s="14" t="n">
@@ -8509,12 +8065,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C18" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D18" s="47" t="n">
+      <c r="D18" s="45" t="n">
         <v>4708.33</v>
       </c>
       <c r="E18" s="14" t="n">
@@ -8541,12 +8097,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C19" s="46" t="inlineStr">
+      <c r="C19" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D19" s="47" t="n">
+      <c r="D19" s="45" t="n">
         <v>4500</v>
       </c>
       <c r="E19" s="14" t="n">
@@ -8573,12 +8129,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C20" s="46" t="inlineStr">
+      <c r="C20" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="D20" s="45" t="n">
         <v>3556.19</v>
       </c>
       <c r="E20" s="14" t="n">
@@ -8605,12 +8161,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C21" s="46" t="inlineStr">
+      <c r="C21" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D21" s="47" t="n">
+      <c r="D21" s="45" t="n">
         <v>2600</v>
       </c>
       <c r="E21" s="14" t="n">
@@ -8637,12 +8193,12 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C22" s="46" t="inlineStr">
+      <c r="C22" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
       </c>
-      <c r="D22" s="47" t="n">
+      <c r="D22" s="45" t="n">
         <v>1835.77</v>
       </c>
       <c r="E22" s="14" t="n">
@@ -8669,12 +8225,12 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C23" s="46" t="inlineStr">
+      <c r="C23" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
       </c>
-      <c r="D23" s="47" t="n">
+      <c r="D23" s="45" t="n">
         <v>1702.29</v>
       </c>
       <c r="E23" s="14" t="n">
@@ -8701,12 +8257,12 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C24" s="46" t="inlineStr">
+      <c r="C24" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
       </c>
-      <c r="D24" s="47" t="n">
+      <c r="D24" s="45" t="n">
         <v>1517.06</v>
       </c>
       <c r="E24" s="14" t="n">
@@ -8733,12 +8289,12 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C25" s="46" t="inlineStr">
+      <c r="C25" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="45" t="n">
         <v>1096.69</v>
       </c>
       <c r="E25" s="14" t="n">
@@ -8765,12 +8321,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C26" s="46" t="inlineStr">
+      <c r="C26" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D26" s="47" t="n">
+      <c r="D26" s="45" t="n">
         <v>1075</v>
       </c>
       <c r="E26" s="14" t="n">
@@ -8797,12 +8353,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C27" s="46" t="inlineStr">
+      <c r="C27" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="45" t="n">
         <v>766.66</v>
       </c>
       <c r="E27" s="14" t="n">
@@ -8829,12 +8385,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C28" s="46" t="inlineStr">
+      <c r="C28" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D28" s="47" t="n">
+      <c r="D28" s="45" t="n">
         <v>638.3</v>
       </c>
       <c r="E28" s="14" t="n">
@@ -8861,12 +8417,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C29" s="46" t="inlineStr">
+      <c r="C29" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D29" s="47" t="n">
+      <c r="D29" s="45" t="n">
         <v>187.51</v>
       </c>
       <c r="E29" s="14" t="n">
@@ -8893,12 +8449,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C30" s="46" t="inlineStr">
+      <c r="C30" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D30" s="47" t="n">
+      <c r="D30" s="45" t="n">
         <v>157.07</v>
       </c>
       <c r="E30" s="14" t="n">
@@ -8925,12 +8481,12 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C31" s="46" t="inlineStr">
+      <c r="C31" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
       </c>
-      <c r="D31" s="47" t="n">
+      <c r="D31" s="45" t="n">
         <v>156.81</v>
       </c>
       <c r="E31" s="14" t="n">
@@ -8957,12 +8513,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C32" s="46" t="inlineStr">
+      <c r="C32" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D32" s="47" t="n">
+      <c r="D32" s="45" t="n">
         <v>50</v>
       </c>
       <c r="E32" s="14" t="n">
@@ -8989,12 +8545,12 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C33" s="46" t="inlineStr">
+      <c r="C33" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D33" s="47" t="n">
+      <c r="D33" s="45" t="n">
         <v>36.54</v>
       </c>
       <c r="E33" s="14" t="n">
@@ -9018,7 +8574,7 @@
       </c>
       <c r="B34" s="20" t="n"/>
       <c r="C34" s="20" t="n"/>
-      <c r="D34" s="48">
+      <c r="D34" s="46">
         <f>SUM(D6:D33)</f>
         <v/>
       </c>
@@ -9185,7 +8741,7 @@
       <c r="E42" s="20" t="n"/>
     </row>
     <row r="44" ht="13" customHeight="1">
-      <c r="A44" s="45" t="inlineStr">
+      <c r="A44" s="43" t="inlineStr">
         <is>
           <t>HOW TO READ OUTSIDE SPENDING</t>
         </is>
@@ -9343,7 +8899,7 @@
         <f>IF(AND(ISNUMBER(B6),ISNUMBER(B22),B22&lt;&gt;0),B6/B22,"")</f>
         <v/>
       </c>
-      <c r="D6" s="49" t="n">
+      <c r="D6" s="47" t="n">
         <v>12</v>
       </c>
       <c r="E6" s="42" t="n">
@@ -9353,7 +8909,7 @@
         <f>IF(AND(ISNUMBER(E6),ISNUMBER(E22),E22&lt;&gt;0),E6/E22,"")</f>
         <v/>
       </c>
-      <c r="G6" s="49" t="n">
+      <c r="G6" s="47" t="n">
         <v>65</v>
       </c>
     </row>
@@ -9370,7 +8926,7 @@
         <f>IF(AND(ISNUMBER(B7),ISNUMBER(B22),B22&lt;&gt;0),B7/B22,"")</f>
         <v/>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="47" t="n">
         <v>169</v>
       </c>
       <c r="E7" s="42" t="n">
@@ -9380,7 +8936,7 @@
         <f>IF(AND(ISNUMBER(E7),ISNUMBER(E22),E22&lt;&gt;0),E7/E22,"")</f>
         <v/>
       </c>
-      <c r="G7" s="49" t="n">
+      <c r="G7" s="47" t="n">
         <v>508</v>
       </c>
     </row>
@@ -9397,7 +8953,7 @@
         <f>IF(AND(ISNUMBER(B8),ISNUMBER(B22),B22&lt;&gt;0),B8/B22,"")</f>
         <v/>
       </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="47" t="n">
         <v>9</v>
       </c>
       <c r="E8" s="42" t="n">
@@ -9407,7 +8963,7 @@
         <f>IF(AND(ISNUMBER(E8),ISNUMBER(E22),E22&lt;&gt;0),E8/E22,"")</f>
         <v/>
       </c>
-      <c r="G8" s="49" t="n">
+      <c r="G8" s="47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9424,7 +8980,7 @@
         <f>IF(AND(ISNUMBER(B9),ISNUMBER(B22),B22&lt;&gt;0),B9/B22,"")</f>
         <v/>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="47" t="n">
         <v>19</v>
       </c>
       <c r="E9" s="42" t="n">
@@ -9434,7 +8990,7 @@
         <f>IF(AND(ISNUMBER(E9),ISNUMBER(E22),E22&lt;&gt;0),E9/E22,"")</f>
         <v/>
       </c>
-      <c r="G9" s="49" t="n">
+      <c r="G9" s="47" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9451,7 +9007,7 @@
         <f>IF(AND(ISNUMBER(B10),ISNUMBER(B22),B22&lt;&gt;0),B10/B22,"")</f>
         <v/>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="47" t="n">
         <v>5</v>
       </c>
       <c r="E10" s="42" t="n">
@@ -9461,7 +9017,7 @@
         <f>IF(AND(ISNUMBER(E10),ISNUMBER(E22),E22&lt;&gt;0),E10/E22,"")</f>
         <v/>
       </c>
-      <c r="G10" s="49" t="n">
+      <c r="G10" s="47" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9478,7 +9034,7 @@
         <f>IF(AND(ISNUMBER(B11),ISNUMBER(B22),B22&lt;&gt;0),B11/B22,"")</f>
         <v/>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="47" t="n">
         <v>8</v>
       </c>
       <c r="E11" s="42" t="n">
@@ -9488,7 +9044,7 @@
         <f>IF(AND(ISNUMBER(E11),ISNUMBER(E22),E22&lt;&gt;0),E11/E22,"")</f>
         <v/>
       </c>
-      <c r="G11" s="49" t="n">
+      <c r="G11" s="47" t="n">
         <v>19</v>
       </c>
     </row>
@@ -9505,7 +9061,7 @@
         <f>IF(AND(ISNUMBER(B12),ISNUMBER(B22),B22&lt;&gt;0),B12/B22,"")</f>
         <v/>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="47" t="n">
         <v>61</v>
       </c>
       <c r="E12" s="42" t="n">
@@ -9515,7 +9071,7 @@
         <f>IF(AND(ISNUMBER(E12),ISNUMBER(E22),E22&lt;&gt;0),E12/E22,"")</f>
         <v/>
       </c>
-      <c r="G12" s="49" t="n">
+      <c r="G12" s="47" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9532,7 +9088,7 @@
         <f>IF(AND(ISNUMBER(B13),ISNUMBER(B22),B22&lt;&gt;0),B13/B22,"")</f>
         <v/>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="47" t="n">
         <v>16</v>
       </c>
       <c r="E13" s="42" t="n">
@@ -9542,7 +9098,7 @@
         <f>IF(AND(ISNUMBER(E13),ISNUMBER(E22),E22&lt;&gt;0),E13/E22,"")</f>
         <v/>
       </c>
-      <c r="G13" s="49" t="n">
+      <c r="G13" s="47" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9559,7 +9115,7 @@
         <f>IF(AND(ISNUMBER(B14),ISNUMBER(B22),B22&lt;&gt;0),B14/B22,"")</f>
         <v/>
       </c>
-      <c r="D14" s="49" t="n">
+      <c r="D14" s="47" t="n">
         <v>48</v>
       </c>
       <c r="E14" s="42" t="n">
@@ -9569,7 +9125,7 @@
         <f>IF(AND(ISNUMBER(E14),ISNUMBER(E22),E22&lt;&gt;0),E14/E22,"")</f>
         <v/>
       </c>
-      <c r="G14" s="49" t="n">
+      <c r="G14" s="47" t="n">
         <v>252</v>
       </c>
     </row>
@@ -9586,7 +9142,7 @@
         <f>IF(AND(ISNUMBER(B15),ISNUMBER(B22),B22&lt;&gt;0),B15/B22,"")</f>
         <v/>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="47" t="n">
         <v>15</v>
       </c>
       <c r="E15" s="42" t="n">
@@ -9596,7 +9152,7 @@
         <f>IF(AND(ISNUMBER(E15),ISNUMBER(E22),E22&lt;&gt;0),E15/E22,"")</f>
         <v/>
       </c>
-      <c r="G15" s="49" t="n">
+      <c r="G15" s="47" t="n">
         <v>105</v>
       </c>
     </row>
@@ -9613,7 +9169,7 @@
         <f>IF(AND(ISNUMBER(B16),ISNUMBER(B22),B22&lt;&gt;0),B16/B22,"")</f>
         <v/>
       </c>
-      <c r="D16" s="49" t="n">
+      <c r="D16" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="42" t="n">
@@ -9623,7 +9179,7 @@
         <f>IF(AND(ISNUMBER(E16),ISNUMBER(E22),E22&lt;&gt;0),E16/E22,"")</f>
         <v/>
       </c>
-      <c r="G16" s="49" t="n">
+      <c r="G16" s="47" t="n">
         <v>51</v>
       </c>
     </row>
@@ -9640,7 +9196,7 @@
         <f>IF(AND(ISNUMBER(B17),ISNUMBER(B22),B22&lt;&gt;0),B17/B22,"")</f>
         <v/>
       </c>
-      <c r="D17" s="49" t="n">
+      <c r="D17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="42" t="n">
@@ -9650,7 +9206,7 @@
         <f>IF(AND(ISNUMBER(E17),ISNUMBER(E22),E22&lt;&gt;0),E17/E22,"")</f>
         <v/>
       </c>
-      <c r="G17" s="49" t="n">
+      <c r="G17" s="47" t="n">
         <v>12</v>
       </c>
     </row>
@@ -9667,7 +9223,7 @@
         <f>IF(AND(ISNUMBER(B18),ISNUMBER(B22),B22&lt;&gt;0),B18/B22,"")</f>
         <v/>
       </c>
-      <c r="D18" s="49" t="n">
+      <c r="D18" s="47" t="n">
         <v>20</v>
       </c>
       <c r="E18" s="42" t="n">
@@ -9677,7 +9233,7 @@
         <f>IF(AND(ISNUMBER(E18),ISNUMBER(E22),E22&lt;&gt;0),E18/E22,"")</f>
         <v/>
       </c>
-      <c r="G18" s="49" t="n">
+      <c r="G18" s="47" t="n">
         <v>91</v>
       </c>
     </row>
@@ -9694,7 +9250,7 @@
         <f>IF(AND(ISNUMBER(B19),ISNUMBER(B22),B22&lt;&gt;0),B19/B22,"")</f>
         <v/>
       </c>
-      <c r="D19" s="49" t="n">
+      <c r="D19" s="47" t="n">
         <v>12</v>
       </c>
       <c r="E19" s="42" t="n">
@@ -9704,7 +9260,7 @@
         <f>IF(AND(ISNUMBER(E19),ISNUMBER(E22),E22&lt;&gt;0),E19/E22,"")</f>
         <v/>
       </c>
-      <c r="G19" s="49" t="n">
+      <c r="G19" s="47" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9721,7 +9277,7 @@
         <f>IF(AND(ISNUMBER(B20),ISNUMBER(B22),B22&lt;&gt;0),B20/B22,"")</f>
         <v/>
       </c>
-      <c r="D20" s="49" t="n">
+      <c r="D20" s="47" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="42" t="n">
@@ -9731,7 +9287,7 @@
         <f>IF(AND(ISNUMBER(E20),ISNUMBER(E22),E22&lt;&gt;0),E20/E22,"")</f>
         <v/>
       </c>
-      <c r="G20" s="49" t="n">
+      <c r="G20" s="47" t="n">
         <v>9</v>
       </c>
     </row>
@@ -9748,7 +9304,7 @@
         <f>IF(AND(ISNUMBER(B21),ISNUMBER(B22),B22&lt;&gt;0),B21/B22,"")</f>
         <v/>
       </c>
-      <c r="D21" s="49" t="n">
+      <c r="D21" s="47" t="n">
         <v>2</v>
       </c>
       <c r="E21" s="42" t="n">
@@ -9758,7 +9314,7 @@
         <f>IF(AND(ISNUMBER(E21),ISNUMBER(E22),E22&lt;&gt;0),E21/E22,"")</f>
         <v/>
       </c>
-      <c r="G21" s="49" t="n">
+      <c r="G21" s="47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9776,7 +9332,7 @@
         <f>IF(AND(ISNUMBER(B22),ISNUMBER(B22),B22&lt;&gt;0),B22/B22,"")</f>
         <v/>
       </c>
-      <c r="D22" s="50">
+      <c r="D22" s="48">
         <f>SUM(D6:D21)</f>
         <v/>
       </c>
@@ -9788,7 +9344,7 @@
         <f>IF(AND(ISNUMBER(E22),ISNUMBER(E22),E22&lt;&gt;0),E22/E22,"")</f>
         <v/>
       </c>
-      <c r="G22" s="50">
+      <c r="G22" s="48">
         <f>SUM(G6:G21)</f>
         <v/>
       </c>
@@ -9863,7 +9419,7 @@
       <c r="B27" s="42" t="n">
         <v>543229</v>
       </c>
-      <c r="C27" s="51" t="n">
+      <c r="C27" s="49" t="n">
         <v>11</v>
       </c>
       <c r="D27" s="14" t="inlineStr">
@@ -9891,7 +9447,7 @@
       <c r="B28" s="42" t="n">
         <v>203646.79</v>
       </c>
-      <c r="C28" s="51" t="n">
+      <c r="C28" s="49" t="n">
         <v>7</v>
       </c>
       <c r="D28" s="14" t="inlineStr">
@@ -9919,7 +9475,7 @@
       <c r="B29" s="42" t="n">
         <v>75187.39999999999</v>
       </c>
-      <c r="C29" s="51" t="n">
+      <c r="C29" s="49" t="n">
         <v>16</v>
       </c>
       <c r="D29" s="14" t="inlineStr">
@@ -9947,7 +9503,7 @@
       <c r="B30" s="42" t="n">
         <v>58673.23</v>
       </c>
-      <c r="C30" s="51" t="n">
+      <c r="C30" s="49" t="n">
         <v>17</v>
       </c>
       <c r="D30" s="14" t="inlineStr">
@@ -9975,7 +9531,7 @@
       <c r="B31" s="42" t="n">
         <v>54920.71</v>
       </c>
-      <c r="C31" s="51" t="n">
+      <c r="C31" s="49" t="n">
         <v>35</v>
       </c>
       <c r="D31" s="14" t="inlineStr">
@@ -10003,7 +9559,7 @@
       <c r="B32" s="42" t="n">
         <v>54605.66</v>
       </c>
-      <c r="C32" s="51" t="n">
+      <c r="C32" s="49" t="n">
         <v>76</v>
       </c>
       <c r="D32" s="14" t="inlineStr">
@@ -10031,7 +9587,7 @@
       <c r="B33" s="42" t="n">
         <v>35000</v>
       </c>
-      <c r="C33" s="51" t="n">
+      <c r="C33" s="49" t="n">
         <v>7</v>
       </c>
       <c r="D33" s="14" t="inlineStr">
@@ -10059,7 +9615,7 @@
       <c r="B34" s="42" t="n">
         <v>34817.13</v>
       </c>
-      <c r="C34" s="51" t="n">
+      <c r="C34" s="49" t="n">
         <v>8</v>
       </c>
       <c r="D34" s="14" t="inlineStr">
@@ -10087,7 +9643,7 @@
       <c r="B35" s="42" t="n">
         <v>31749.04</v>
       </c>
-      <c r="C35" s="51" t="n">
+      <c r="C35" s="49" t="n">
         <v>5</v>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -10115,7 +9671,7 @@
       <c r="B36" s="42" t="n">
         <v>26182.97</v>
       </c>
-      <c r="C36" s="51" t="n">
+      <c r="C36" s="49" t="n">
         <v>9</v>
       </c>
       <c r="D36" s="14" t="inlineStr">
@@ -10143,7 +9699,7 @@
       <c r="B37" s="42" t="n">
         <v>22312</v>
       </c>
-      <c r="C37" s="51" t="n">
+      <c r="C37" s="49" t="n">
         <v>8</v>
       </c>
       <c r="D37" s="14" t="inlineStr">
@@ -10171,7 +9727,7 @@
       <c r="B38" s="42" t="n">
         <v>17832.07</v>
       </c>
-      <c r="C38" s="51" t="n">
+      <c r="C38" s="49" t="n">
         <v>12</v>
       </c>
       <c r="D38" s="14" t="inlineStr">
@@ -10199,7 +9755,7 @@
       <c r="B39" s="42" t="n">
         <v>15000</v>
       </c>
-      <c r="C39" s="51" t="n">
+      <c r="C39" s="49" t="n">
         <v>3</v>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -10227,7 +9783,7 @@
       <c r="B40" s="42" t="n">
         <v>15000</v>
       </c>
-      <c r="C40" s="51" t="n">
+      <c r="C40" s="49" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="14" t="inlineStr">
@@ -10255,7 +9811,7 @@
       <c r="B41" s="42" t="n">
         <v>14003.2</v>
       </c>
-      <c r="C41" s="51" t="n">
+      <c r="C41" s="49" t="n">
         <v>3</v>
       </c>
       <c r="D41" s="14" t="inlineStr">
@@ -10329,7 +9885,7 @@
       <c r="B45" s="42" t="n">
         <v>332817.9</v>
       </c>
-      <c r="C45" s="51" t="n">
+      <c r="C45" s="49" t="n">
         <v>107</v>
       </c>
       <c r="D45" s="14" t="inlineStr">
@@ -10357,7 +9913,7 @@
       <c r="B46" s="42" t="n">
         <v>166301.16</v>
       </c>
-      <c r="C46" s="51" t="n">
+      <c r="C46" s="49" t="n">
         <v>10</v>
       </c>
       <c r="D46" s="14" t="inlineStr">
@@ -10385,7 +9941,7 @@
       <c r="B47" s="42" t="n">
         <v>132892.75</v>
       </c>
-      <c r="C47" s="51" t="n">
+      <c r="C47" s="49" t="n">
         <v>27</v>
       </c>
       <c r="D47" s="14" t="inlineStr">
@@ -10413,7 +9969,7 @@
       <c r="B48" s="42" t="n">
         <v>74152.92</v>
       </c>
-      <c r="C48" s="51" t="n">
+      <c r="C48" s="49" t="n">
         <v>31</v>
       </c>
       <c r="D48" s="14" t="inlineStr">
@@ -10441,7 +9997,7 @@
       <c r="B49" s="42" t="n">
         <v>64451.03</v>
       </c>
-      <c r="C49" s="51" t="n">
+      <c r="C49" s="49" t="n">
         <v>16</v>
       </c>
       <c r="D49" s="14" t="inlineStr">
@@ -10469,7 +10025,7 @@
       <c r="B50" s="42" t="n">
         <v>52876.5</v>
       </c>
-      <c r="C50" s="51" t="n">
+      <c r="C50" s="49" t="n">
         <v>15</v>
       </c>
       <c r="D50" s="14" t="inlineStr">
@@ -10497,7 +10053,7 @@
       <c r="B51" s="42" t="n">
         <v>43138.83</v>
       </c>
-      <c r="C51" s="51" t="n">
+      <c r="C51" s="49" t="n">
         <v>28</v>
       </c>
       <c r="D51" s="14" t="inlineStr">
@@ -10525,7 +10081,7 @@
       <c r="B52" s="42" t="n">
         <v>41412.94</v>
       </c>
-      <c r="C52" s="51" t="n">
+      <c r="C52" s="49" t="n">
         <v>83</v>
       </c>
       <c r="D52" s="14" t="inlineStr">
@@ -10553,7 +10109,7 @@
       <c r="B53" s="42" t="n">
         <v>40643.9</v>
       </c>
-      <c r="C53" s="51" t="n">
+      <c r="C53" s="49" t="n">
         <v>10</v>
       </c>
       <c r="D53" s="14" t="inlineStr">
@@ -10581,7 +10137,7 @@
       <c r="B54" s="42" t="n">
         <v>38124.5</v>
       </c>
-      <c r="C54" s="51" t="n">
+      <c r="C54" s="49" t="n">
         <v>2</v>
       </c>
       <c r="D54" s="14" t="inlineStr">
@@ -10609,7 +10165,7 @@
       <c r="B55" s="42" t="n">
         <v>36592.58</v>
       </c>
-      <c r="C55" s="51" t="n">
+      <c r="C55" s="49" t="n">
         <v>18</v>
       </c>
       <c r="D55" s="14" t="inlineStr">
@@ -10637,7 +10193,7 @@
       <c r="B56" s="42" t="n">
         <v>25875</v>
       </c>
-      <c r="C56" s="51" t="n">
+      <c r="C56" s="49" t="n">
         <v>5</v>
       </c>
       <c r="D56" s="14" t="inlineStr">
@@ -10665,7 +10221,7 @@
       <c r="B57" s="42" t="n">
         <v>24000</v>
       </c>
-      <c r="C57" s="51" t="n">
+      <c r="C57" s="49" t="n">
         <v>8</v>
       </c>
       <c r="D57" s="14" t="inlineStr">
@@ -10693,7 +10249,7 @@
       <c r="B58" s="42" t="n">
         <v>20586.36</v>
       </c>
-      <c r="C58" s="51" t="n">
+      <c r="C58" s="49" t="n">
         <v>18</v>
       </c>
       <c r="D58" s="14" t="inlineStr">
@@ -10721,7 +10277,7 @@
       <c r="B59" s="42" t="n">
         <v>20183.55</v>
       </c>
-      <c r="C59" s="51" t="n">
+      <c r="C59" s="49" t="n">
         <v>36</v>
       </c>
       <c r="D59" s="14" t="inlineStr">
@@ -10795,7 +10351,7 @@
         <f>IF(AND(ISNUMBER(B63),ISNUMBER(B22),B22&lt;&gt;0),B63/B22,"")</f>
         <v/>
       </c>
-      <c r="D63" s="52" t="n"/>
+      <c r="D63" s="50" t="n"/>
       <c r="E63" s="42" t="n">
         <v>459357.16</v>
       </c>
@@ -10803,7 +10359,7 @@
         <f>IF(AND(ISNUMBER(E63),ISNUMBER(E22),E22&lt;&gt;0),E63/E22,"")</f>
         <v/>
       </c>
-      <c r="G63" s="52" t="n"/>
+      <c r="G63" s="50" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
@@ -10818,7 +10374,7 @@
         <f>IF(AND(ISNUMBER(B64),ISNUMBER(B22),B22&lt;&gt;0),B64/B22,"")</f>
         <v/>
       </c>
-      <c r="D64" s="52" t="n"/>
+      <c r="D64" s="50" t="n"/>
       <c r="E64" s="42" t="n">
         <v>242504.01</v>
       </c>
@@ -10826,7 +10382,7 @@
         <f>IF(AND(ISNUMBER(E64),ISNUMBER(E22),E22&lt;&gt;0),E64/E22,"")</f>
         <v/>
       </c>
-      <c r="G64" s="52" t="n"/>
+      <c r="G64" s="50" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
@@ -10841,7 +10397,7 @@
         <f>IF(AND(ISNUMBER(B65),ISNUMBER(B22),B22&lt;&gt;0),B65/B22,"")</f>
         <v/>
       </c>
-      <c r="D65" s="52" t="n"/>
+      <c r="D65" s="50" t="n"/>
       <c r="E65" s="42" t="n">
         <v>335283.52</v>
       </c>
@@ -10849,7 +10405,7 @@
         <f>IF(AND(ISNUMBER(E65),ISNUMBER(E22),E22&lt;&gt;0),E65/E22,"")</f>
         <v/>
       </c>
-      <c r="G65" s="52" t="n"/>
+      <c r="G65" s="50" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
@@ -10864,7 +10420,7 @@
         <f>IF(AND(ISNUMBER(B66),ISNUMBER(B22),B22&lt;&gt;0),B66/B22,"")</f>
         <v/>
       </c>
-      <c r="D66" s="52" t="n"/>
+      <c r="D66" s="50" t="n"/>
       <c r="E66" s="42" t="n">
         <v>317942.8</v>
       </c>
@@ -10872,7 +10428,7 @@
         <f>IF(AND(ISNUMBER(E66),ISNUMBER(E22),E22&lt;&gt;0),E66/E22,"")</f>
         <v/>
       </c>
-      <c r="G66" s="52" t="n"/>
+      <c r="G66" s="50" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
@@ -10887,7 +10443,7 @@
         <f>IF(AND(ISNUMBER(B67),ISNUMBER(B22),B22&lt;&gt;0),B67/B22,"")</f>
         <v/>
       </c>
-      <c r="D67" s="52" t="n"/>
+      <c r="D67" s="50" t="n"/>
       <c r="E67" s="42" t="n">
         <v>17435.36</v>
       </c>
@@ -10895,7 +10451,7 @@
         <f>IF(AND(ISNUMBER(E67),ISNUMBER(E22),E22&lt;&gt;0),E67/E22,"")</f>
         <v/>
       </c>
-      <c r="G67" s="52" t="n"/>
+      <c r="G67" s="50" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
@@ -10910,7 +10466,7 @@
         <f>IF(AND(ISNUMBER(B68),ISNUMBER(B22),B22&lt;&gt;0),B68/B22,"")</f>
         <v/>
       </c>
-      <c r="D68" s="52" t="n"/>
+      <c r="D68" s="50" t="n"/>
       <c r="E68" s="42" t="n">
         <v>7613.56</v>
       </c>
@@ -10918,7 +10474,7 @@
         <f>IF(AND(ISNUMBER(E68),ISNUMBER(E22),E22&lt;&gt;0),E68/E22,"")</f>
         <v/>
       </c>
-      <c r="G68" s="52" t="n"/>
+      <c r="G68" s="50" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
@@ -10933,7 +10489,7 @@
         <f>IF(AND(ISNUMBER(B69),ISNUMBER(B22),B22&lt;&gt;0),B69/B22,"")</f>
         <v/>
       </c>
-      <c r="D69" s="52" t="n"/>
+      <c r="D69" s="50" t="n"/>
       <c r="E69" s="42" t="n">
         <v>15050.7</v>
       </c>
@@ -10941,7 +10497,7 @@
         <f>IF(AND(ISNUMBER(E69),ISNUMBER(E22),E22&lt;&gt;0),E69/E22,"")</f>
         <v/>
       </c>
-      <c r="G69" s="52" t="n"/>
+      <c r="G69" s="50" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
@@ -10956,7 +10512,7 @@
         <f>IF(AND(ISNUMBER(B70),ISNUMBER(B22),B22&lt;&gt;0),B70/B22,"")</f>
         <v/>
       </c>
-      <c r="D70" s="52" t="n"/>
+      <c r="D70" s="50" t="n"/>
       <c r="E70" s="42" t="n">
         <v>14439.86</v>
       </c>
@@ -10964,7 +10520,7 @@
         <f>IF(AND(ISNUMBER(E70),ISNUMBER(E22),E22&lt;&gt;0),E70/E22,"")</f>
         <v/>
       </c>
-      <c r="G70" s="52" t="n"/>
+      <c r="G70" s="50" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
@@ -10979,7 +10535,7 @@
         <f>IF(AND(ISNUMBER(B71),ISNUMBER(B22),B22&lt;&gt;0),B71/B22,"")</f>
         <v/>
       </c>
-      <c r="D71" s="52" t="n"/>
+      <c r="D71" s="50" t="n"/>
       <c r="E71" s="42" t="n">
         <v>77783.67999999999</v>
       </c>
@@ -10987,7 +10543,7 @@
         <f>IF(AND(ISNUMBER(E71),ISNUMBER(E22),E22&lt;&gt;0),E71/E22,"")</f>
         <v/>
       </c>
-      <c r="G71" s="52" t="n"/>
+      <c r="G71" s="50" t="n"/>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="32" t="inlineStr">
@@ -11108,7 +10664,7 @@
         <f>IF(AND(ISNUMBER(B6),ISNUMBER(B17),B17&lt;&gt;0),B6/B17,"")</f>
         <v/>
       </c>
-      <c r="D6" s="49" t="n">
+      <c r="D6" s="47" t="n">
         <v>687</v>
       </c>
       <c r="E6" s="42" t="n">
@@ -11118,7 +10674,7 @@
         <f>IF(AND(ISNUMBER(E6),ISNUMBER(E17),E17&lt;&gt;0),E6/E17,"")</f>
         <v/>
       </c>
-      <c r="G6" s="49" t="n">
+      <c r="G6" s="47" t="n">
         <v>1185</v>
       </c>
     </row>
@@ -11135,7 +10691,7 @@
         <f>IF(AND(ISNUMBER(B7),ISNUMBER(B17),B17&lt;&gt;0),B7/B17,"")</f>
         <v/>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="47" t="n">
         <v>42</v>
       </c>
       <c r="E7" s="42" t="n">
@@ -11145,7 +10701,7 @@
         <f>IF(AND(ISNUMBER(E7),ISNUMBER(E17),E17&lt;&gt;0),E7/E17,"")</f>
         <v/>
       </c>
-      <c r="G7" s="49" t="n">
+      <c r="G7" s="47" t="n">
         <v>1923</v>
       </c>
     </row>
@@ -11162,7 +10718,7 @@
         <f>IF(AND(ISNUMBER(B8),ISNUMBER(B17),B17&lt;&gt;0),B8/B17,"")</f>
         <v/>
       </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="47" t="n">
         <v>206</v>
       </c>
       <c r="E8" s="42" t="n">
@@ -11172,7 +10728,7 @@
         <f>IF(AND(ISNUMBER(E8),ISNUMBER(E17),E17&lt;&gt;0),E8/E17,"")</f>
         <v/>
       </c>
-      <c r="G8" s="49" t="n">
+      <c r="G8" s="47" t="n">
         <v>420</v>
       </c>
     </row>
@@ -11189,7 +10745,7 @@
         <f>IF(AND(ISNUMBER(B9),ISNUMBER(B17),B17&lt;&gt;0),B9/B17,"")</f>
         <v/>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="47" t="n">
         <v>317</v>
       </c>
       <c r="E9" s="42" t="n">
@@ -11199,7 +10755,7 @@
         <f>IF(AND(ISNUMBER(E9),ISNUMBER(E17),E17&lt;&gt;0),E9/E17,"")</f>
         <v/>
       </c>
-      <c r="G9" s="49" t="n">
+      <c r="G9" s="47" t="n">
         <v>1371</v>
       </c>
     </row>
@@ -11216,7 +10772,7 @@
         <f>IF(AND(ISNUMBER(B10),ISNUMBER(B17),B17&lt;&gt;0),B10/B17,"")</f>
         <v/>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="47" t="n">
         <v>14</v>
       </c>
       <c r="E10" s="42" t="n">
@@ -11226,7 +10782,7 @@
         <f>IF(AND(ISNUMBER(E10),ISNUMBER(E17),E17&lt;&gt;0),E10/E17,"")</f>
         <v/>
       </c>
-      <c r="G10" s="49" t="n">
+      <c r="G10" s="47" t="n">
         <v>2187</v>
       </c>
     </row>
@@ -11243,7 +10799,7 @@
         <f>IF(AND(ISNUMBER(B11),ISNUMBER(B17),B17&lt;&gt;0),B11/B17,"")</f>
         <v/>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="47" t="n">
         <v>254</v>
       </c>
       <c r="E11" s="42" t="n">
@@ -11253,7 +10809,7 @@
         <f>IF(AND(ISNUMBER(E11),ISNUMBER(E17),E17&lt;&gt;0),E11/E17,"")</f>
         <v/>
       </c>
-      <c r="G11" s="49" t="n">
+      <c r="G11" s="47" t="n">
         <v>65</v>
       </c>
     </row>
@@ -11270,7 +10826,7 @@
         <f>IF(AND(ISNUMBER(B12),ISNUMBER(B17),B17&lt;&gt;0),B12/B17,"")</f>
         <v/>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="47" t="n">
         <v>43</v>
       </c>
       <c r="E12" s="42" t="n">
@@ -11280,7 +10836,7 @@
         <f>IF(AND(ISNUMBER(E12),ISNUMBER(E17),E17&lt;&gt;0),E12/E17,"")</f>
         <v/>
       </c>
-      <c r="G12" s="49" t="n">
+      <c r="G12" s="47" t="n">
         <v>404</v>
       </c>
     </row>
@@ -11297,7 +10853,7 @@
         <f>IF(AND(ISNUMBER(B13),ISNUMBER(B17),B17&lt;&gt;0),B13/B17,"")</f>
         <v/>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="42" t="n">
@@ -11307,7 +10863,7 @@
         <f>IF(AND(ISNUMBER(E13),ISNUMBER(E17),E17&lt;&gt;0),E13/E17,"")</f>
         <v/>
       </c>
-      <c r="G13" s="49" t="n">
+      <c r="G13" s="47" t="n">
         <v>230</v>
       </c>
     </row>
@@ -11324,7 +10880,7 @@
         <f>IF(AND(ISNUMBER(B14),ISNUMBER(B17),B17&lt;&gt;0),B14/B17,"")</f>
         <v/>
       </c>
-      <c r="D14" s="49" t="n">
+      <c r="D14" s="47" t="n">
         <v>72</v>
       </c>
       <c r="E14" s="42" t="n">
@@ -11334,7 +10890,7 @@
         <f>IF(AND(ISNUMBER(E14),ISNUMBER(E17),E17&lt;&gt;0),E14/E17,"")</f>
         <v/>
       </c>
-      <c r="G14" s="49" t="n">
+      <c r="G14" s="47" t="n">
         <v>432</v>
       </c>
     </row>
@@ -11351,7 +10907,7 @@
         <f>IF(AND(ISNUMBER(B15),ISNUMBER(B17),B17&lt;&gt;0),B15/B17,"")</f>
         <v/>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="47" t="n">
         <v>41</v>
       </c>
       <c r="E15" s="42" t="n">
@@ -11361,7 +10917,7 @@
         <f>IF(AND(ISNUMBER(E15),ISNUMBER(E17),E17&lt;&gt;0),E15/E17,"")</f>
         <v/>
       </c>
-      <c r="G15" s="49" t="n">
+      <c r="G15" s="47" t="n">
         <v>98</v>
       </c>
     </row>
@@ -11378,7 +10934,7 @@
         <f>IF(AND(ISNUMBER(B16),ISNUMBER(B17),B17&lt;&gt;0),B16/B17,"")</f>
         <v/>
       </c>
-      <c r="D16" s="49" t="n">
+      <c r="D16" s="47" t="n">
         <v>473</v>
       </c>
       <c r="E16" s="42" t="n">
@@ -11388,7 +10944,7 @@
         <f>IF(AND(ISNUMBER(E16),ISNUMBER(E17),E17&lt;&gt;0),E16/E17,"")</f>
         <v/>
       </c>
-      <c r="G16" s="49" t="n">
+      <c r="G16" s="47" t="n">
         <v>4931</v>
       </c>
     </row>
@@ -11406,7 +10962,7 @@
         <f>IF(AND(ISNUMBER(B17),ISNUMBER(B17),B17&lt;&gt;0),B17/B17,"")</f>
         <v/>
       </c>
-      <c r="D17" s="50">
+      <c r="D17" s="48">
         <f>SUM(D6:D16)</f>
         <v/>
       </c>
@@ -11418,7 +10974,7 @@
         <f>IF(AND(ISNUMBER(E17),ISNUMBER(E17),E17&lt;&gt;0),E17/E17,"")</f>
         <v/>
       </c>
-      <c r="G17" s="50">
+      <c r="G17" s="48">
         <f>SUM(G6:G16)</f>
         <v/>
       </c>
@@ -11486,7 +11042,7 @@
         <f>IF(AND(ISNUMBER(B21),ISNUMBER(B26),B26&lt;&gt;0),B21/B26,"")</f>
         <v/>
       </c>
-      <c r="D21" s="49" t="n"/>
+      <c r="D21" s="47" t="n"/>
       <c r="E21" s="42" t="n">
         <v>734290.36</v>
       </c>
@@ -11494,7 +11050,7 @@
         <f>IF(AND(ISNUMBER(E21),ISNUMBER(E26),E26&lt;&gt;0),E21/E26,"")</f>
         <v/>
       </c>
-      <c r="G21" s="49" t="n"/>
+      <c r="G21" s="47" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -11509,7 +11065,7 @@
         <f>IF(AND(ISNUMBER(B22),ISNUMBER(B26),B26&lt;&gt;0),B22/B26,"")</f>
         <v/>
       </c>
-      <c r="D22" s="49" t="n">
+      <c r="D22" s="47" t="n">
         <v>453</v>
       </c>
       <c r="E22" s="42" t="n">
@@ -11519,7 +11075,7 @@
         <f>IF(AND(ISNUMBER(E22),ISNUMBER(E26),E26&lt;&gt;0),E22/E26,"")</f>
         <v/>
       </c>
-      <c r="G22" s="49" t="n">
+      <c r="G22" s="47" t="n">
         <v>372</v>
       </c>
     </row>
@@ -11536,7 +11092,7 @@
         <f>IF(AND(ISNUMBER(B23),ISNUMBER(B26),B26&lt;&gt;0),B23/B26,"")</f>
         <v/>
       </c>
-      <c r="D23" s="49" t="n">
+      <c r="D23" s="47" t="n">
         <v>292</v>
       </c>
       <c r="E23" s="42" t="n">
@@ -11546,7 +11102,7 @@
         <f>IF(AND(ISNUMBER(E23),ISNUMBER(E26),E26&lt;&gt;0),E23/E26,"")</f>
         <v/>
       </c>
-      <c r="G23" s="49" t="n">
+      <c r="G23" s="47" t="n">
         <v>443</v>
       </c>
     </row>
@@ -11563,7 +11119,7 @@
         <f>IF(AND(ISNUMBER(B24),ISNUMBER(B26),B26&lt;&gt;0),B24/B26,"")</f>
         <v/>
       </c>
-      <c r="D24" s="49" t="n">
+      <c r="D24" s="47" t="n">
         <v>224</v>
       </c>
       <c r="E24" s="42" t="n">
@@ -11573,7 +11129,7 @@
         <f>IF(AND(ISNUMBER(E24),ISNUMBER(E26),E26&lt;&gt;0),E24/E26,"")</f>
         <v/>
       </c>
-      <c r="G24" s="49" t="n">
+      <c r="G24" s="47" t="n">
         <v>482</v>
       </c>
     </row>
@@ -11590,7 +11146,7 @@
         <f>IF(AND(ISNUMBER(B25),ISNUMBER(B26),B26&lt;&gt;0),B25/B26,"")</f>
         <v/>
       </c>
-      <c r="D25" s="49" t="n">
+      <c r="D25" s="47" t="n">
         <v>246</v>
       </c>
       <c r="E25" s="42" t="n">
@@ -11600,7 +11156,7 @@
         <f>IF(AND(ISNUMBER(E25),ISNUMBER(E26),E26&lt;&gt;0),E25/E26,"")</f>
         <v/>
       </c>
-      <c r="G25" s="49" t="n">
+      <c r="G25" s="47" t="n">
         <v>607</v>
       </c>
     </row>
@@ -11687,7 +11243,7 @@
         <f>IF(AND(ISNUMBER(B31),ISNUMBER(B33),B33&lt;&gt;0),B31/B33,"")</f>
         <v/>
       </c>
-      <c r="D31" s="52" t="n"/>
+      <c r="D31" s="50" t="n"/>
       <c r="E31" s="42" t="n">
         <v>395259.46</v>
       </c>
@@ -11695,7 +11251,7 @@
         <f>IF(AND(ISNUMBER(E31),ISNUMBER(E33),E33&lt;&gt;0),E31/E33,"")</f>
         <v/>
       </c>
-      <c r="G31" s="52" t="n"/>
+      <c r="G31" s="50" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -11711,7 +11267,7 @@
         <f>IF(AND(ISNUMBER(B32),ISNUMBER(B33),B33&lt;&gt;0),B32/B33,"")</f>
         <v/>
       </c>
-      <c r="D32" s="52" t="n"/>
+      <c r="D32" s="50" t="n"/>
       <c r="E32" s="40">
         <f>IF(AND(ISNUMBER(E31),ISNUMBER(E33)),E33-E31,"")</f>
         <v/>
@@ -11720,7 +11276,7 @@
         <f>IF(AND(ISNUMBER(E32),ISNUMBER(E33),E33&lt;&gt;0),E32/E33,"")</f>
         <v/>
       </c>
-      <c r="G32" s="52" t="n"/>
+      <c r="G32" s="50" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
@@ -11728,7 +11284,7 @@
           <t>TOTAL itemized, by zip</t>
         </is>
       </c>
-      <c r="B33" s="53" t="n">
+      <c r="B33" s="51" t="n">
         <v>1362106.16</v>
       </c>
       <c r="C33" s="37">
@@ -11736,7 +11292,7 @@
         <v/>
       </c>
       <c r="D33" s="20" t="n"/>
-      <c r="E33" s="53" t="n">
+      <c r="E33" s="51" t="n">
         <v>2944555.07</v>
       </c>
       <c r="F33" s="37">
@@ -11795,7 +11351,7 @@
       <c r="B38" s="42" t="n">
         <v>453408.96</v>
       </c>
-      <c r="C38" s="49" t="n">
+      <c r="C38" s="47" t="n">
         <v>950</v>
       </c>
     </row>
@@ -11808,7 +11364,7 @@
       <c r="B39" s="42" t="n">
         <v>112066.52</v>
       </c>
-      <c r="C39" s="49" t="n">
+      <c r="C39" s="47" t="n">
         <v>121</v>
       </c>
     </row>
@@ -11821,7 +11377,7 @@
       <c r="B40" s="42" t="n">
         <v>98780.55</v>
       </c>
-      <c r="C40" s="49" t="n">
+      <c r="C40" s="47" t="n">
         <v>118</v>
       </c>
     </row>
@@ -11834,7 +11390,7 @@
       <c r="B41" s="42" t="n">
         <v>58164.13</v>
       </c>
-      <c r="C41" s="49" t="n">
+      <c r="C41" s="47" t="n">
         <v>77</v>
       </c>
     </row>
@@ -11847,7 +11403,7 @@
       <c r="B42" s="42" t="n">
         <v>44343.9</v>
       </c>
-      <c r="C42" s="49" t="n">
+      <c r="C42" s="47" t="n">
         <v>21</v>
       </c>
     </row>
@@ -11860,7 +11416,7 @@
       <c r="B43" s="42" t="n">
         <v>26135.41</v>
       </c>
-      <c r="C43" s="49" t="n">
+      <c r="C43" s="47" t="n">
         <v>38</v>
       </c>
     </row>
@@ -11873,7 +11429,7 @@
       <c r="B44" s="42" t="n">
         <v>25304</v>
       </c>
-      <c r="C44" s="49" t="n">
+      <c r="C44" s="47" t="n">
         <v>86</v>
       </c>
     </row>
@@ -11886,7 +11442,7 @@
       <c r="B45" s="42" t="n">
         <v>25083.33</v>
       </c>
-      <c r="C45" s="49" t="n">
+      <c r="C45" s="47" t="n">
         <v>53</v>
       </c>
     </row>
@@ -11899,7 +11455,7 @@
       <c r="B46" s="42" t="n">
         <v>22300</v>
       </c>
-      <c r="C46" s="49" t="n">
+      <c r="C46" s="47" t="n">
         <v>23</v>
       </c>
     </row>
@@ -11912,7 +11468,7 @@
       <c r="B47" s="42" t="n">
         <v>20900</v>
       </c>
-      <c r="C47" s="49" t="n">
+      <c r="C47" s="47" t="n">
         <v>17</v>
       </c>
     </row>
@@ -11959,7 +11515,7 @@
       <c r="B51" s="42" t="n">
         <v>757056.16</v>
       </c>
-      <c r="C51" s="49" t="n">
+      <c r="C51" s="47" t="n">
         <v>10536</v>
       </c>
     </row>
@@ -11972,7 +11528,7 @@
       <c r="B52" s="42" t="n">
         <v>309337.13</v>
       </c>
-      <c r="C52" s="49" t="n">
+      <c r="C52" s="47" t="n">
         <v>275</v>
       </c>
     </row>
@@ -11985,7 +11541,7 @@
       <c r="B53" s="42" t="n">
         <v>169174.26</v>
       </c>
-      <c r="C53" s="49" t="n">
+      <c r="C53" s="47" t="n">
         <v>142</v>
       </c>
     </row>
@@ -11998,7 +11554,7 @@
       <c r="B54" s="42" t="n">
         <v>126323.31</v>
       </c>
-      <c r="C54" s="49" t="n">
+      <c r="C54" s="47" t="n">
         <v>75</v>
       </c>
     </row>
@@ -12011,7 +11567,7 @@
       <c r="B55" s="42" t="n">
         <v>124651.54</v>
       </c>
-      <c r="C55" s="49" t="n">
+      <c r="C55" s="47" t="n">
         <v>94</v>
       </c>
     </row>
@@ -12024,7 +11580,7 @@
       <c r="B56" s="42" t="n">
         <v>107698.83</v>
       </c>
-      <c r="C56" s="49" t="n">
+      <c r="C56" s="47" t="n">
         <v>71</v>
       </c>
     </row>
@@ -12037,7 +11593,7 @@
       <c r="B57" s="42" t="n">
         <v>105830.87</v>
       </c>
-      <c r="C57" s="49" t="n">
+      <c r="C57" s="47" t="n">
         <v>51</v>
       </c>
     </row>
@@ -12050,7 +11606,7 @@
       <c r="B58" s="42" t="n">
         <v>76092.81</v>
       </c>
-      <c r="C58" s="49" t="n">
+      <c r="C58" s="47" t="n">
         <v>49</v>
       </c>
     </row>
@@ -12063,7 +11619,7 @@
       <c r="B59" s="42" t="n">
         <v>75497.97</v>
       </c>
-      <c r="C59" s="49" t="n">
+      <c r="C59" s="47" t="n">
         <v>58</v>
       </c>
     </row>
@@ -12076,7 +11632,7 @@
       <c r="B60" s="42" t="n">
         <v>68701.13</v>
       </c>
-      <c r="C60" s="49" t="n">
+      <c r="C60" s="47" t="n">
         <v>67</v>
       </c>
     </row>
@@ -12191,7 +11747,7 @@
         <f>IFERROR(B6/$H$114,"")</f>
         <v/>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="52">
         <f>COUNTIFS($I$20:$I$113,A6)</f>
         <v/>
       </c>
@@ -12210,7 +11766,7 @@
         <f>IFERROR(B7/$H$114,"")</f>
         <v/>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="52">
         <f>COUNTIFS($I$20:$I$113,A7)</f>
         <v/>
       </c>
@@ -12229,7 +11785,7 @@
         <f>IFERROR(B8/$H$114,"")</f>
         <v/>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="52">
         <f>COUNTIFS($I$20:$I$113,A8)</f>
         <v/>
       </c>
@@ -12248,7 +11804,7 @@
         <f>IFERROR(B9/$H$114,"")</f>
         <v/>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="52">
         <f>COUNTIFS($I$20:$I$113,A9)</f>
         <v/>
       </c>
@@ -12267,7 +11823,7 @@
         <f>IFERROR(B10/$H$114,"")</f>
         <v/>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="52">
         <f>COUNTIFS($I$20:$I$113,A10)</f>
         <v/>
       </c>
@@ -12286,7 +11842,7 @@
         <f>IFERROR(B11/$H$114,"")</f>
         <v/>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="52">
         <f>COUNTIFS($I$20:$I$113,A11)</f>
         <v/>
       </c>
@@ -12305,7 +11861,7 @@
         <f>IFERROR(B12/$H$114,"")</f>
         <v/>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="52">
         <f>COUNTIFS($I$20:$I$113,A12)</f>
         <v/>
       </c>
@@ -12324,7 +11880,7 @@
         <f>IFERROR(B13/$H$114,"")</f>
         <v/>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="52">
         <f>COUNTIFS($I$20:$I$113,A13)</f>
         <v/>
       </c>
@@ -12343,7 +11899,7 @@
         <f>IFERROR(B14/$H$114,"")</f>
         <v/>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="52">
         <f>COUNTIFS($I$20:$I$113,A14)</f>
         <v/>
       </c>
@@ -12359,7 +11915,7 @@
         <v/>
       </c>
       <c r="C15" s="20" t="n"/>
-      <c r="D15" s="50">
+      <c r="D15" s="48">
         <f>SUM(D6:D14)</f>
         <v/>
       </c>
@@ -12443,7 +11999,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C20" s="46" t="inlineStr">
+      <c r="C20" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -12468,7 +12024,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H20" s="47" t="n">
+      <c r="H20" s="45" t="n">
         <v>306418</v>
       </c>
       <c r="I20" s="14" t="inlineStr">
@@ -12493,7 +12049,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C21" s="46" t="inlineStr">
+      <c r="C21" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -12518,7 +12074,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H21" s="47" t="n">
+      <c r="H21" s="45" t="n">
         <v>272247</v>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -12543,7 +12099,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C22" s="46" t="inlineStr">
+      <c r="C22" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -12568,7 +12124,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H22" s="47" t="n">
+      <c r="H22" s="45" t="n">
         <v>249750</v>
       </c>
       <c r="I22" s="14" t="inlineStr">
@@ -12593,7 +12149,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C23" s="46" t="inlineStr">
+      <c r="C23" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -12618,7 +12174,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H23" s="47" t="n">
+      <c r="H23" s="45" t="n">
         <v>175000</v>
       </c>
       <c r="I23" s="14" t="inlineStr">
@@ -12643,7 +12199,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C24" s="46" t="inlineStr">
+      <c r="C24" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -12668,7 +12224,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H24" s="47" t="n">
+      <c r="H24" s="45" t="n">
         <v>154509</v>
       </c>
       <c r="I24" s="14" t="inlineStr">
@@ -12693,7 +12249,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C25" s="46" t="inlineStr">
+      <c r="C25" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -12718,7 +12274,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H25" s="47" t="n">
+      <c r="H25" s="45" t="n">
         <v>150000</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -12743,7 +12299,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C26" s="46" t="inlineStr">
+      <c r="C26" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -12768,7 +12324,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H26" s="47" t="n">
+      <c r="H26" s="45" t="n">
         <v>128000</v>
       </c>
       <c r="I26" s="14" t="inlineStr">
@@ -12793,7 +12349,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C27" s="46" t="inlineStr">
+      <c r="C27" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -12818,7 +12374,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H27" s="47" t="n">
+      <c r="H27" s="45" t="n">
         <v>110000</v>
       </c>
       <c r="I27" s="14" t="inlineStr">
@@ -12843,7 +12399,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C28" s="46" t="inlineStr">
+      <c r="C28" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -12868,7 +12424,7 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="H28" s="47" t="n">
+      <c r="H28" s="45" t="n">
         <v>106756.66</v>
       </c>
       <c r="I28" s="14" t="inlineStr">
@@ -12893,7 +12449,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C29" s="46" t="inlineStr">
+      <c r="C29" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -12918,7 +12474,7 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="H29" s="47" t="n">
+      <c r="H29" s="45" t="n">
         <v>102333.33</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
@@ -12943,7 +12499,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C30" s="46" t="inlineStr">
+      <c r="C30" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -12968,7 +12524,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H30" s="47" t="n">
+      <c r="H30" s="45" t="n">
         <v>95000</v>
       </c>
       <c r="I30" s="14" t="inlineStr">
@@ -12993,7 +12549,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C31" s="46" t="inlineStr">
+      <c r="C31" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13018,7 +12574,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H31" s="47" t="n">
+      <c r="H31" s="45" t="n">
         <v>90000</v>
       </c>
       <c r="I31" s="14" t="inlineStr">
@@ -13043,7 +12599,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C32" s="46" t="inlineStr">
+      <c r="C32" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13068,7 +12624,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H32" s="47" t="n">
+      <c r="H32" s="45" t="n">
         <v>83120</v>
       </c>
       <c r="I32" s="14" t="inlineStr">
@@ -13093,7 +12649,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C33" s="46" t="inlineStr">
+      <c r="C33" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13118,7 +12674,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H33" s="47" t="n">
+      <c r="H33" s="45" t="n">
         <v>80000</v>
       </c>
       <c r="I33" s="14" t="inlineStr">
@@ -13143,7 +12699,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C34" s="46" t="inlineStr">
+      <c r="C34" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -13168,7 +12724,7 @@
           <t>FL</t>
         </is>
       </c>
-      <c r="H34" s="47" t="n">
+      <c r="H34" s="45" t="n">
         <v>66666.67</v>
       </c>
       <c r="I34" s="14" t="inlineStr">
@@ -13193,7 +12749,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C35" s="46" t="inlineStr">
+      <c r="C35" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13218,7 +12774,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H35" s="47" t="n">
+      <c r="H35" s="45" t="n">
         <v>52120</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -13243,7 +12799,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C36" s="46" t="inlineStr">
+      <c r="C36" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13268,7 +12824,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H36" s="47" t="n">
+      <c r="H36" s="45" t="n">
         <v>50500</v>
       </c>
       <c r="I36" s="14" t="inlineStr">
@@ -13293,7 +12849,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C37" s="46" t="inlineStr">
+      <c r="C37" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13318,7 +12874,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H37" s="47" t="n">
+      <c r="H37" s="45" t="n">
         <v>46000</v>
       </c>
       <c r="I37" s="14" t="inlineStr">
@@ -13343,7 +12899,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C38" s="46" t="inlineStr">
+      <c r="C38" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13368,7 +12924,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H38" s="47" t="n">
+      <c r="H38" s="45" t="n">
         <v>45110</v>
       </c>
       <c r="I38" s="14" t="inlineStr">
@@ -13393,7 +12949,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C39" s="46" t="inlineStr">
+      <c r="C39" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13418,7 +12974,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H39" s="47" t="n">
+      <c r="H39" s="45" t="n">
         <v>28000</v>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -13443,7 +12999,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C40" s="46" t="inlineStr">
+      <c r="C40" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13468,7 +13024,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H40" s="47" t="n">
+      <c r="H40" s="45" t="n">
         <v>28000</v>
       </c>
       <c r="I40" s="14" t="inlineStr">
@@ -13493,7 +13049,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C41" s="46" t="inlineStr">
+      <c r="C41" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13518,7 +13074,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H41" s="47" t="n">
+      <c r="H41" s="45" t="n">
         <v>25500</v>
       </c>
       <c r="I41" s="14" t="inlineStr">
@@ -13543,7 +13099,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C42" s="46" t="inlineStr">
+      <c r="C42" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13568,7 +13124,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H42" s="47" t="n">
+      <c r="H42" s="45" t="n">
         <v>25226.25</v>
       </c>
       <c r="I42" s="14" t="inlineStr">
@@ -13593,7 +13149,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C43" s="46" t="inlineStr">
+      <c r="C43" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13618,7 +13174,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H43" s="47" t="n">
+      <c r="H43" s="45" t="n">
         <v>25000</v>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -13643,7 +13199,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C44" s="46" t="inlineStr">
+      <c r="C44" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13668,7 +13224,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H44" s="47" t="n">
+      <c r="H44" s="45" t="n">
         <v>25000</v>
       </c>
       <c r="I44" s="14" t="inlineStr">
@@ -13693,7 +13249,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C45" s="46" t="inlineStr">
+      <c r="C45" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13718,7 +13274,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H45" s="47" t="n">
+      <c r="H45" s="45" t="n">
         <v>23584.25</v>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -13743,7 +13299,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C46" s="46" t="inlineStr">
+      <c r="C46" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13768,7 +13324,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H46" s="47" t="n">
+      <c r="H46" s="45" t="n">
         <v>21000</v>
       </c>
       <c r="I46" s="14" t="inlineStr">
@@ -13793,7 +13349,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C47" s="46" t="inlineStr">
+      <c r="C47" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13818,7 +13374,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H47" s="47" t="n">
+      <c r="H47" s="45" t="n">
         <v>19755.5</v>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -13843,7 +13399,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C48" s="46" t="inlineStr">
+      <c r="C48" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13868,7 +13424,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H48" s="47" t="n">
+      <c r="H48" s="45" t="n">
         <v>19755.5</v>
       </c>
       <c r="I48" s="14" t="inlineStr">
@@ -13893,7 +13449,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C49" s="46" t="inlineStr">
+      <c r="C49" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13918,7 +13474,7 @@
           <t>IL</t>
         </is>
       </c>
-      <c r="H49" s="47" t="n">
+      <c r="H49" s="45" t="n">
         <v>12300</v>
       </c>
       <c r="I49" s="14" t="inlineStr">
@@ -13943,7 +13499,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C50" s="46" t="inlineStr">
+      <c r="C50" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -13968,7 +13524,7 @@
           <t>NY</t>
         </is>
       </c>
-      <c r="H50" s="47" t="n">
+      <c r="H50" s="45" t="n">
         <v>12062</v>
       </c>
       <c r="I50" s="14" t="inlineStr">
@@ -13993,7 +13549,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C51" s="46" t="inlineStr">
+      <c r="C51" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14018,7 +13574,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H51" s="47" t="n">
+      <c r="H51" s="45" t="n">
         <v>11510</v>
       </c>
       <c r="I51" s="14" t="inlineStr">
@@ -14043,7 +13599,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C52" s="46" t="inlineStr">
+      <c r="C52" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14068,7 +13624,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H52" s="47" t="n">
+      <c r="H52" s="45" t="n">
         <v>10000</v>
       </c>
       <c r="I52" s="14" t="inlineStr">
@@ -14093,7 +13649,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C53" s="46" t="inlineStr">
+      <c r="C53" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -14118,7 +13674,7 @@
           <t>FL</t>
         </is>
       </c>
-      <c r="H53" s="47" t="n">
+      <c r="H53" s="45" t="n">
         <v>9161.42</v>
       </c>
       <c r="I53" s="14" t="inlineStr">
@@ -14143,7 +13699,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C54" s="46" t="inlineStr">
+      <c r="C54" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -14168,7 +13724,7 @@
           <t>FL</t>
         </is>
       </c>
-      <c r="H54" s="47" t="n">
+      <c r="H54" s="45" t="n">
         <v>9154.690000000001</v>
       </c>
       <c r="I54" s="14" t="inlineStr">
@@ -14193,7 +13749,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C55" s="46" t="inlineStr">
+      <c r="C55" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -14218,7 +13774,7 @@
           <t>FL</t>
         </is>
       </c>
-      <c r="H55" s="47" t="n">
+      <c r="H55" s="45" t="n">
         <v>9153.559999999999</v>
       </c>
       <c r="I55" s="14" t="inlineStr">
@@ -14243,7 +13799,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C56" s="46" t="inlineStr">
+      <c r="C56" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -14268,7 +13824,7 @@
           <t>FL</t>
         </is>
       </c>
-      <c r="H56" s="47" t="n">
+      <c r="H56" s="45" t="n">
         <v>9145.43</v>
       </c>
       <c r="I56" s="14" t="inlineStr">
@@ -14293,7 +13849,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C57" s="46" t="inlineStr">
+      <c r="C57" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14318,7 +13874,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H57" s="47" t="n">
+      <c r="H57" s="45" t="n">
         <v>9116.67</v>
       </c>
       <c r="I57" s="14" t="inlineStr">
@@ -14343,7 +13899,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C58" s="46" t="inlineStr">
+      <c r="C58" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14368,7 +13924,7 @@
           <t>NY</t>
         </is>
       </c>
-      <c r="H58" s="47" t="n">
+      <c r="H58" s="45" t="n">
         <v>6405</v>
       </c>
       <c r="I58" s="14" t="inlineStr">
@@ -14393,7 +13949,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C59" s="46" t="inlineStr">
+      <c r="C59" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -14418,7 +13974,7 @@
           <t>TX</t>
         </is>
       </c>
-      <c r="H59" s="47" t="n">
+      <c r="H59" s="45" t="n">
         <v>6044</v>
       </c>
       <c r="I59" s="14" t="inlineStr">
@@ -14443,7 +13999,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C60" s="46" t="inlineStr">
+      <c r="C60" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14468,7 +14024,7 @@
           <t>IL</t>
         </is>
       </c>
-      <c r="H60" s="47" t="n">
+      <c r="H60" s="45" t="n">
         <v>4625</v>
       </c>
       <c r="I60" s="14" t="inlineStr">
@@ -14493,7 +14049,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C61" s="46" t="inlineStr">
+      <c r="C61" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14518,7 +14074,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H61" s="47" t="n">
+      <c r="H61" s="45" t="n">
         <v>4250</v>
       </c>
       <c r="I61" s="14" t="inlineStr">
@@ -14543,7 +14099,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C62" s="46" t="inlineStr">
+      <c r="C62" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14568,7 +14124,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H62" s="47" t="n">
+      <c r="H62" s="45" t="n">
         <v>4000</v>
       </c>
       <c r="I62" s="14" t="inlineStr">
@@ -14593,7 +14149,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C63" s="46" t="inlineStr">
+      <c r="C63" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14618,7 +14174,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H63" s="47" t="n">
+      <c r="H63" s="45" t="n">
         <v>3766.66</v>
       </c>
       <c r="I63" s="14" t="inlineStr">
@@ -14643,7 +14199,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C64" s="46" t="inlineStr">
+      <c r="C64" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14668,7 +14224,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H64" s="47" t="n">
+      <c r="H64" s="45" t="n">
         <v>3625</v>
       </c>
       <c r="I64" s="14" t="inlineStr">
@@ -14693,7 +14249,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C65" s="46" t="inlineStr">
+      <c r="C65" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14718,7 +14274,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H65" s="47" t="n">
+      <c r="H65" s="45" t="n">
         <v>3556.19</v>
       </c>
       <c r="I65" s="14" t="inlineStr">
@@ -14743,7 +14299,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C66" s="46" t="inlineStr">
+      <c r="C66" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14768,7 +14324,7 @@
           <t>DC</t>
         </is>
       </c>
-      <c r="H66" s="47" t="n">
+      <c r="H66" s="45" t="n">
         <v>3300</v>
       </c>
       <c r="I66" s="14" t="inlineStr">
@@ -14793,7 +14349,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C67" s="46" t="inlineStr">
+      <c r="C67" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14818,7 +14374,7 @@
           <t>NY</t>
         </is>
       </c>
-      <c r="H67" s="47" t="n">
+      <c r="H67" s="45" t="n">
         <v>3160.5</v>
       </c>
       <c r="I67" s="14" t="inlineStr">
@@ -14843,7 +14399,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C68" s="46" t="inlineStr">
+      <c r="C68" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14868,7 +14424,7 @@
           <t>NY</t>
         </is>
       </c>
-      <c r="H68" s="47" t="n">
+      <c r="H68" s="45" t="n">
         <v>3118.5</v>
       </c>
       <c r="I68" s="14" t="inlineStr">
@@ -14893,7 +14449,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C69" s="46" t="inlineStr">
+      <c r="C69" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -14918,7 +14474,7 @@
           <t>NY</t>
         </is>
       </c>
-      <c r="H69" s="47" t="n">
+      <c r="H69" s="45" t="n">
         <v>2940</v>
       </c>
       <c r="I69" s="14" t="inlineStr">
@@ -14943,7 +14499,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C70" s="46" t="inlineStr">
+      <c r="C70" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -14968,7 +14524,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H70" s="47" t="n">
+      <c r="H70" s="45" t="n">
         <v>2040</v>
       </c>
       <c r="I70" s="14" t="inlineStr">
@@ -14993,7 +14549,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C71" s="46" t="inlineStr">
+      <c r="C71" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -15018,7 +14574,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H71" s="47" t="n">
+      <c r="H71" s="45" t="n">
         <v>1700</v>
       </c>
       <c r="I71" s="14" t="inlineStr">
@@ -15043,7 +14599,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C72" s="46" t="inlineStr">
+      <c r="C72" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -15068,7 +14624,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H72" s="47" t="n">
+      <c r="H72" s="45" t="n">
         <v>1700</v>
       </c>
       <c r="I72" s="14" t="inlineStr">
@@ -15093,7 +14649,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C73" s="46" t="inlineStr">
+      <c r="C73" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -15118,7 +14674,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H73" s="47" t="n">
+      <c r="H73" s="45" t="n">
         <v>1700</v>
       </c>
       <c r="I73" s="14" t="inlineStr">
@@ -15143,7 +14699,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C74" s="46" t="inlineStr">
+      <c r="C74" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -15168,7 +14724,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H74" s="47" t="n">
+      <c r="H74" s="45" t="n">
         <v>1700</v>
       </c>
       <c r="I74" s="14" t="inlineStr">
@@ -15193,7 +14749,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C75" s="46" t="inlineStr">
+      <c r="C75" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -15218,7 +14774,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H75" s="47" t="n">
+      <c r="H75" s="45" t="n">
         <v>1600</v>
       </c>
       <c r="I75" s="14" t="inlineStr">
@@ -15243,7 +14799,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C76" s="46" t="inlineStr">
+      <c r="C76" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -15268,7 +14824,7 @@
           <t>OH</t>
         </is>
       </c>
-      <c r="H76" s="47" t="n">
+      <c r="H76" s="45" t="n">
         <v>1517.06</v>
       </c>
       <c r="I76" s="14" t="inlineStr">
@@ -15293,7 +14849,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C77" s="46" t="inlineStr">
+      <c r="C77" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -15318,7 +14874,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H77" s="47" t="n">
+      <c r="H77" s="45" t="n">
         <v>1421.27</v>
       </c>
       <c r="I77" s="14" t="inlineStr">
@@ -15343,7 +14899,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C78" s="46" t="inlineStr">
+      <c r="C78" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -15368,7 +14924,7 @@
           <t>DC</t>
         </is>
       </c>
-      <c r="H78" s="47" t="n">
+      <c r="H78" s="45" t="n">
         <v>1230.12</v>
       </c>
       <c r="I78" s="14" t="inlineStr">
@@ -15393,7 +14949,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C79" s="46" t="inlineStr">
+      <c r="C79" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -15418,7 +14974,7 @@
           <t>NY</t>
         </is>
       </c>
-      <c r="H79" s="47" t="n">
+      <c r="H79" s="45" t="n">
         <v>1200</v>
       </c>
       <c r="I79" s="14" t="inlineStr">
@@ -15443,7 +14999,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C80" s="46" t="inlineStr">
+      <c r="C80" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -15468,7 +15024,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H80" s="47" t="n">
+      <c r="H80" s="45" t="n">
         <v>1175</v>
       </c>
       <c r="I80" s="14" t="inlineStr">
@@ -15493,7 +15049,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C81" s="46" t="inlineStr">
+      <c r="C81" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -15518,7 +15074,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H81" s="47" t="n">
+      <c r="H81" s="45" t="n">
         <v>1083.33</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
@@ -15543,7 +15099,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C82" s="46" t="inlineStr">
+      <c r="C82" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -15568,7 +15124,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H82" s="47" t="n">
+      <c r="H82" s="45" t="n">
         <v>1012.5</v>
       </c>
       <c r="I82" s="14" t="inlineStr">
@@ -15593,7 +15149,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C83" s="46" t="inlineStr">
+      <c r="C83" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -15618,7 +15174,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H83" s="47" t="n">
+      <c r="H83" s="45" t="n">
         <v>1000</v>
       </c>
       <c r="I83" s="14" t="inlineStr">
@@ -15643,7 +15199,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C84" s="46" t="inlineStr">
+      <c r="C84" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -15668,7 +15224,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H84" s="47" t="n">
+      <c r="H84" s="45" t="n">
         <v>883.34</v>
       </c>
       <c r="I84" s="14" t="inlineStr">
@@ -15693,7 +15249,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C85" s="46" t="inlineStr">
+      <c r="C85" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -15718,7 +15274,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H85" s="47" t="n">
+      <c r="H85" s="45" t="n">
         <v>859.88</v>
       </c>
       <c r="I85" s="14" t="inlineStr">
@@ -15743,7 +15299,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C86" s="46" t="inlineStr">
+      <c r="C86" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -15768,7 +15324,7 @@
           <t>NY</t>
         </is>
       </c>
-      <c r="H86" s="47" t="n">
+      <c r="H86" s="45" t="n">
         <v>735</v>
       </c>
       <c r="I86" s="14" t="inlineStr">
@@ -15793,7 +15349,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C87" s="46" t="inlineStr">
+      <c r="C87" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -15818,7 +15374,7 @@
           <t>NY</t>
         </is>
       </c>
-      <c r="H87" s="47" t="n">
+      <c r="H87" s="45" t="n">
         <v>682</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
@@ -15843,7 +15399,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C88" s="46" t="inlineStr">
+      <c r="C88" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -15868,7 +15424,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H88" s="47" t="n">
+      <c r="H88" s="45" t="n">
         <v>666.66</v>
       </c>
       <c r="I88" s="14" t="inlineStr">
@@ -15893,7 +15449,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C89" s="46" t="inlineStr">
+      <c r="C89" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -15918,7 +15474,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H89" s="47" t="n">
+      <c r="H89" s="45" t="n">
         <v>638.3</v>
       </c>
       <c r="I89" s="14" t="inlineStr">
@@ -15943,7 +15499,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C90" s="46" t="inlineStr">
+      <c r="C90" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -15968,7 +15524,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H90" s="47" t="n">
+      <c r="H90" s="45" t="n">
         <v>346</v>
       </c>
       <c r="I90" s="14" t="inlineStr">
@@ -15993,7 +15549,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C91" s="46" t="inlineStr">
+      <c r="C91" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16018,7 +15574,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H91" s="47" t="n">
+      <c r="H91" s="45" t="n">
         <v>304.22</v>
       </c>
       <c r="I91" s="14" t="inlineStr">
@@ -16043,7 +15599,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C92" s="46" t="inlineStr">
+      <c r="C92" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16068,7 +15624,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H92" s="47" t="n">
+      <c r="H92" s="45" t="n">
         <v>284</v>
       </c>
       <c r="I92" s="14" t="inlineStr">
@@ -16093,7 +15649,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C93" s="46" t="inlineStr">
+      <c r="C93" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16118,7 +15674,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H93" s="47" t="n">
+      <c r="H93" s="45" t="n">
         <v>250.82</v>
       </c>
       <c r="I93" s="14" t="inlineStr">
@@ -16143,7 +15699,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C94" s="46" t="inlineStr">
+      <c r="C94" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16168,7 +15724,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H94" s="47" t="n">
+      <c r="H94" s="45" t="n">
         <v>243</v>
       </c>
       <c r="I94" s="14" t="inlineStr">
@@ -16193,7 +15749,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C95" s="46" t="inlineStr">
+      <c r="C95" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16218,7 +15774,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H95" s="47" t="n">
+      <c r="H95" s="45" t="n">
         <v>236.81</v>
       </c>
       <c r="I95" s="14" t="inlineStr">
@@ -16243,7 +15799,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C96" s="46" t="inlineStr">
+      <c r="C96" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16268,7 +15824,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H96" s="47" t="n">
+      <c r="H96" s="45" t="n">
         <v>194.64</v>
       </c>
       <c r="I96" s="14" t="inlineStr">
@@ -16293,7 +15849,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C97" s="46" t="inlineStr">
+      <c r="C97" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -16318,7 +15874,7 @@
           <t>GA</t>
         </is>
       </c>
-      <c r="H97" s="47" t="n">
+      <c r="H97" s="45" t="n">
         <v>187.51</v>
       </c>
       <c r="I97" s="14" t="inlineStr">
@@ -16343,7 +15899,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C98" s="46" t="inlineStr">
+      <c r="C98" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -16368,7 +15924,7 @@
           <t>OH</t>
         </is>
       </c>
-      <c r="H98" s="47" t="n">
+      <c r="H98" s="45" t="n">
         <v>157.07</v>
       </c>
       <c r="I98" s="14" t="inlineStr">
@@ -16393,7 +15949,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C99" s="46" t="inlineStr">
+      <c r="C99" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16418,7 +15974,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H99" s="47" t="n">
+      <c r="H99" s="45" t="n">
         <v>156</v>
       </c>
       <c r="I99" s="14" t="inlineStr">
@@ -16443,7 +15999,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C100" s="46" t="inlineStr">
+      <c r="C100" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16468,7 +16024,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H100" s="47" t="n">
+      <c r="H100" s="45" t="n">
         <v>137.49</v>
       </c>
       <c r="I100" s="14" t="inlineStr">
@@ -16493,7 +16049,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C101" s="46" t="inlineStr">
+      <c r="C101" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16518,7 +16074,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H101" s="47" t="n">
+      <c r="H101" s="45" t="n">
         <v>124.9</v>
       </c>
       <c r="I101" s="14" t="inlineStr">
@@ -16543,7 +16099,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C102" s="46" t="inlineStr">
+      <c r="C102" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -16568,7 +16124,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H102" s="47" t="n">
+      <c r="H102" s="45" t="n">
         <v>100</v>
       </c>
       <c r="I102" s="14" t="inlineStr">
@@ -16593,7 +16149,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C103" s="46" t="inlineStr">
+      <c r="C103" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16618,7 +16174,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H103" s="47" t="n">
+      <c r="H103" s="45" t="n">
         <v>96.45</v>
       </c>
       <c r="I103" s="14" t="inlineStr">
@@ -16643,7 +16199,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C104" s="46" t="inlineStr">
+      <c r="C104" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16668,7 +16224,7 @@
           <t>NY</t>
         </is>
       </c>
-      <c r="H104" s="47" t="n">
+      <c r="H104" s="45" t="n">
         <v>85.38</v>
       </c>
       <c r="I104" s="14" t="inlineStr">
@@ -16693,7 +16249,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C105" s="46" t="inlineStr">
+      <c r="C105" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16718,7 +16274,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H105" s="47" t="n">
+      <c r="H105" s="45" t="n">
         <v>76.42</v>
       </c>
       <c r="I105" s="14" t="inlineStr">
@@ -16743,7 +16299,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C106" s="46" t="inlineStr">
+      <c r="C106" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16768,7 +16324,7 @@
           <t>NY</t>
         </is>
       </c>
-      <c r="H106" s="47" t="n">
+      <c r="H106" s="45" t="n">
         <v>71.43000000000001</v>
       </c>
       <c r="I106" s="14" t="inlineStr">
@@ -16793,7 +16349,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C107" s="46" t="inlineStr">
+      <c r="C107" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -16818,7 +16374,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="H107" s="47" t="n">
+      <c r="H107" s="45" t="n">
         <v>62.5</v>
       </c>
       <c r="I107" s="14" t="inlineStr">
@@ -16843,7 +16399,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C108" s="46" t="inlineStr">
+      <c r="C108" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16868,7 +16424,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H108" s="47" t="n">
+      <c r="H108" s="45" t="n">
         <v>55</v>
       </c>
       <c r="I108" s="14" t="inlineStr">
@@ -16893,7 +16449,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C109" s="46" t="inlineStr">
+      <c r="C109" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -16918,7 +16474,7 @@
           <t>DC</t>
         </is>
       </c>
-      <c r="H109" s="47" t="n">
+      <c r="H109" s="45" t="n">
         <v>50</v>
       </c>
       <c r="I109" s="14" t="inlineStr">
@@ -16943,7 +16499,7 @@
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="C110" s="46" t="inlineStr">
+      <c r="C110" s="44" t="inlineStr">
         <is>
           <t>Opposes</t>
         </is>
@@ -16968,7 +16524,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="H110" s="47" t="n">
+      <c r="H110" s="45" t="n">
         <v>39</v>
       </c>
       <c r="I110" s="14" t="inlineStr">
@@ -16993,7 +16549,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C111" s="46" t="inlineStr">
+      <c r="C111" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -17018,7 +16574,7 @@
           <t>PA</t>
         </is>
       </c>
-      <c r="H111" s="47" t="n">
+      <c r="H111" s="45" t="n">
         <v>35.68</v>
       </c>
       <c r="I111" s="14" t="inlineStr">
@@ -17043,7 +16599,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C112" s="46" t="inlineStr">
+      <c r="C112" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -17068,7 +16624,7 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="H112" s="47" t="n">
+      <c r="H112" s="45" t="n">
         <v>32</v>
       </c>
       <c r="I112" s="14" t="inlineStr">
@@ -17093,7 +16649,7 @@
           <t>Bob Brooks</t>
         </is>
       </c>
-      <c r="C113" s="46" t="inlineStr">
+      <c r="C113" s="44" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
@@ -17118,7 +16674,7 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="H113" s="47" t="n">
+      <c r="H113" s="45" t="n">
         <v>4.54</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
@@ -17144,7 +16700,7 @@
       <c r="E114" s="20" t="n"/>
       <c r="F114" s="20" t="n"/>
       <c r="G114" s="20" t="n"/>
-      <c r="H114" s="48">
+      <c r="H114" s="46">
         <f>SUM(H20:H113)</f>
         <v/>
       </c>
@@ -17335,100 +16891,100 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="n">
+      <c r="A6" s="53" t="n">
         <v>2018</v>
       </c>
-      <c r="B6" s="55" t="inlineStr">
+      <c r="B6" s="53" t="inlineStr">
         <is>
           <t>2018-11-06</t>
         </is>
       </c>
-      <c r="C6" s="56" t="inlineStr">
+      <c r="C6" s="54" t="inlineStr">
         <is>
           <t>2018 PA Supreme Court remap (Lehigh Valley: Lehigh, Northampton, s. Monroe)</t>
         </is>
       </c>
-      <c r="D6" s="55" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>Susan Wild</t>
         </is>
       </c>
-      <c r="E6" s="57" t="inlineStr">
+      <c r="E6" s="55" t="inlineStr">
         <is>
           <t>DEM</t>
         </is>
       </c>
-      <c r="F6" s="58" t="inlineStr">
+      <c r="F6" s="56" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="G6" s="59" t="n">
+      <c r="G6" s="57" t="n">
         <v>3320188.01</v>
       </c>
-      <c r="H6" s="59" t="n">
+      <c r="H6" s="57" t="n">
         <v>3294280.32</v>
       </c>
-      <c r="I6" s="59" t="n">
+      <c r="I6" s="57" t="n">
         <v>25907.69</v>
       </c>
-      <c r="J6" s="59" t="n">
+      <c r="J6" s="57" t="n">
         <v>2216364.61</v>
       </c>
-      <c r="K6" s="59" t="n">
+      <c r="K6" s="57" t="n">
         <v>535757.8199999999</v>
       </c>
-      <c r="L6" s="59" t="n">
+      <c r="L6" s="57" t="n">
         <v>558727.21</v>
       </c>
-      <c r="M6" s="59" t="n">
+      <c r="M6" s="57" t="n">
         <v>221405.25</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="58">
         <f>IF(ISNUMBER(G6),G6+L6+SUMIFS($M$6:$M$13,$A$6:$A$13,$A6,$E$6:$E$13,"&lt;&gt;"&amp;$E6),"")</f>
         <v/>
       </c>
-      <c r="O6" s="61" t="n">
+      <c r="O6" s="59" t="n">
         <v>140813</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="60">
         <f>IF(AND(ISNUMBER(O6),SUMIFS($O$6:$O$13,$A$6:$A$13,$A6)&lt;&gt;0),O6/SUMIFS($O$6:$O$13,$A$6:$A$13,$A6),"")</f>
         <v/>
       </c>
-      <c r="Q6" s="63" t="inlineStr">
+      <c r="Q6" s="61" t="inlineStr">
         <is>
           <t>won</t>
         </is>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="62">
         <f>IF(AND(ISNUMBER(G6),ISNUMBER(O6),O6&lt;&gt;0),G6/O6,"")</f>
         <v/>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="62">
         <f>IF(AND(ISNUMBER(N6),ISNUMBER(O6),O6&lt;&gt;0),N6/O6,"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="n">
+      <c r="A7" s="49" t="n">
         <v>2018</v>
       </c>
-      <c r="B7" s="51" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>2018-11-06</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="63" t="inlineStr">
         <is>
           <t>2018 PA Supreme Court remap (Lehigh Valley: Lehigh, Northampton, s. Monroe)</t>
         </is>
       </c>
-      <c r="D7" s="51" t="inlineStr">
+      <c r="D7" s="49" t="inlineStr">
         <is>
           <t>Marty Nothstein</t>
         </is>
       </c>
-      <c r="E7" s="66" t="inlineStr">
+      <c r="E7" s="64" t="inlineStr">
         <is>
           <t>REP</t>
         </is>
@@ -17463,122 +17019,122 @@
         <f>IF(ISNUMBER(G7),G7+L7+SUMIFS($M$6:$M$13,$A$6:$A$13,$A7,$E$6:$E$13,"&lt;&gt;"&amp;$E7),"")</f>
         <v/>
       </c>
-      <c r="O7" s="49" t="n">
+      <c r="O7" s="47" t="n">
         <v>114437</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="65">
         <f>IF(AND(ISNUMBER(O7),SUMIFS($O$6:$O$13,$A$6:$A$13,$A7)&lt;&gt;0),O7/SUMIFS($O$6:$O$13,$A$6:$A$13,$A7),"")</f>
         <v/>
       </c>
-      <c r="Q7" s="68" t="inlineStr">
+      <c r="Q7" s="66" t="inlineStr">
         <is>
           <t>lost</t>
         </is>
       </c>
-      <c r="R7" s="69">
+      <c r="R7" s="67">
         <f>IF(AND(ISNUMBER(G7),ISNUMBER(O7),O7&lt;&gt;0),G7/O7,"")</f>
         <v/>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="67">
         <f>IF(AND(ISNUMBER(N7),ISNUMBER(O7),O7&lt;&gt;0),N7/O7,"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="55" t="n">
+      <c r="A8" s="53" t="n">
         <v>2020</v>
       </c>
-      <c r="B8" s="55" t="inlineStr">
+      <c r="B8" s="53" t="inlineStr">
         <is>
           <t>2020-11-03</t>
         </is>
       </c>
-      <c r="C8" s="56" t="inlineStr">
+      <c r="C8" s="54" t="inlineStr">
         <is>
           <t>2018 PA Supreme Court remap (Lehigh Valley: Lehigh, Northampton, s. Monroe)</t>
         </is>
       </c>
-      <c r="D8" s="55" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>Susan Wild</t>
         </is>
       </c>
-      <c r="E8" s="57" t="inlineStr">
+      <c r="E8" s="55" t="inlineStr">
         <is>
           <t>DEM</t>
         </is>
       </c>
-      <c r="F8" s="58" t="inlineStr">
+      <c r="F8" s="56" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G8" s="59" t="n">
+      <c r="G8" s="57" t="n">
         <v>4644289.9</v>
       </c>
-      <c r="H8" s="59" t="n">
+      <c r="H8" s="57" t="n">
         <v>4591501.23</v>
       </c>
-      <c r="I8" s="59" t="n">
+      <c r="I8" s="57" t="n">
         <v>78696.36</v>
       </c>
-      <c r="J8" s="59" t="n">
+      <c r="J8" s="57" t="n">
         <v>3417373.86</v>
       </c>
-      <c r="K8" s="59" t="n">
+      <c r="K8" s="57" t="n">
         <v>1027681.99</v>
       </c>
-      <c r="L8" s="59" t="n">
+      <c r="L8" s="57" t="n">
         <v>50133.76</v>
       </c>
-      <c r="M8" s="59" t="n">
+      <c r="M8" s="57" t="n">
         <v>127595.71</v>
       </c>
-      <c r="N8" s="60">
+      <c r="N8" s="58">
         <f>IF(ISNUMBER(G8),G8+L8+SUMIFS($M$6:$M$13,$A$6:$A$13,$A8,$E$6:$E$13,"&lt;&gt;"&amp;$E8),"")</f>
         <v/>
       </c>
-      <c r="O8" s="61" t="n">
+      <c r="O8" s="59" t="n">
         <v>195475</v>
       </c>
-      <c r="P8" s="62">
+      <c r="P8" s="60">
         <f>IF(AND(ISNUMBER(O8),SUMIFS($O$6:$O$13,$A$6:$A$13,$A8)&lt;&gt;0),O8/SUMIFS($O$6:$O$13,$A$6:$A$13,$A8),"")</f>
         <v/>
       </c>
-      <c r="Q8" s="63" t="inlineStr">
+      <c r="Q8" s="61" t="inlineStr">
         <is>
           <t>won</t>
         </is>
       </c>
-      <c r="R8" s="64">
+      <c r="R8" s="62">
         <f>IF(AND(ISNUMBER(G8),ISNUMBER(O8),O8&lt;&gt;0),G8/O8,"")</f>
         <v/>
       </c>
-      <c r="S8" s="64">
+      <c r="S8" s="62">
         <f>IF(AND(ISNUMBER(N8),ISNUMBER(O8),O8&lt;&gt;0),N8/O8,"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="n">
+      <c r="A9" s="49" t="n">
         <v>2020</v>
       </c>
-      <c r="B9" s="51" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>2020-11-03</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
+      <c r="C9" s="63" t="inlineStr">
         <is>
           <t>2018 PA Supreme Court remap (Lehigh Valley: Lehigh, Northampton, s. Monroe)</t>
         </is>
       </c>
-      <c r="D9" s="51" t="inlineStr">
+      <c r="D9" s="49" t="inlineStr">
         <is>
           <t>Lisa Scheller</t>
         </is>
       </c>
-      <c r="E9" s="66" t="inlineStr">
+      <c r="E9" s="64" t="inlineStr">
         <is>
           <t>REP</t>
         </is>
@@ -17613,122 +17169,122 @@
         <f>IF(ISNUMBER(G9),G9+L9+SUMIFS($M$6:$M$13,$A$6:$A$13,$A9,$E$6:$E$13,"&lt;&gt;"&amp;$E9),"")</f>
         <v/>
       </c>
-      <c r="O9" s="49" t="n">
+      <c r="O9" s="47" t="n">
         <v>181407</v>
       </c>
-      <c r="P9" s="67">
+      <c r="P9" s="65">
         <f>IF(AND(ISNUMBER(O9),SUMIFS($O$6:$O$13,$A$6:$A$13,$A9)&lt;&gt;0),O9/SUMIFS($O$6:$O$13,$A$6:$A$13,$A9),"")</f>
         <v/>
       </c>
-      <c r="Q9" s="68" t="inlineStr">
+      <c r="Q9" s="66" t="inlineStr">
         <is>
           <t>lost</t>
         </is>
       </c>
-      <c r="R9" s="69">
+      <c r="R9" s="67">
         <f>IF(AND(ISNUMBER(G9),ISNUMBER(O9),O9&lt;&gt;0),G9/O9,"")</f>
         <v/>
       </c>
-      <c r="S9" s="69">
+      <c r="S9" s="67">
         <f>IF(AND(ISNUMBER(N9),ISNUMBER(O9),O9&lt;&gt;0),N9/O9,"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="55" t="n">
+      <c r="A10" s="53" t="n">
         <v>2022</v>
       </c>
-      <c r="B10" s="55" t="inlineStr">
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="C10" s="56" t="inlineStr">
+      <c r="C10" s="54" t="inlineStr">
         <is>
           <t>2022 post-census remap (Lehigh, Northampton, Carbon, part of Monroe)</t>
         </is>
       </c>
-      <c r="D10" s="55" t="inlineStr">
+      <c r="D10" s="53" t="inlineStr">
         <is>
           <t>Susan Wild</t>
         </is>
       </c>
-      <c r="E10" s="57" t="inlineStr">
+      <c r="E10" s="55" t="inlineStr">
         <is>
           <t>DEM</t>
         </is>
       </c>
-      <c r="F10" s="58" t="inlineStr">
+      <c r="F10" s="56" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G10" s="59" t="n">
+      <c r="G10" s="57" t="n">
         <v>7002291.19</v>
       </c>
-      <c r="H10" s="59" t="n">
+      <c r="H10" s="57" t="n">
         <v>7027026.2</v>
       </c>
-      <c r="I10" s="59" t="n">
+      <c r="I10" s="57" t="n">
         <v>53961.35</v>
       </c>
-      <c r="J10" s="59" t="n">
+      <c r="J10" s="57" t="n">
         <v>5366116.25</v>
       </c>
-      <c r="K10" s="59" t="n">
+      <c r="K10" s="57" t="n">
         <v>1279735.82</v>
       </c>
-      <c r="L10" s="59" t="n">
+      <c r="L10" s="57" t="n">
         <v>654900.95</v>
       </c>
-      <c r="M10" s="59" t="n">
+      <c r="M10" s="57" t="n">
         <v>10853652.49</v>
       </c>
-      <c r="N10" s="60">
+      <c r="N10" s="58">
         <f>IF(ISNUMBER(G10),G10+L10+SUMIFS($M$6:$M$13,$A$6:$A$13,$A10,$E$6:$E$13,"&lt;&gt;"&amp;$E10),"")</f>
         <v/>
       </c>
-      <c r="O10" s="61" t="n">
+      <c r="O10" s="59" t="n">
         <v>151364</v>
       </c>
-      <c r="P10" s="62">
+      <c r="P10" s="60">
         <f>IF(AND(ISNUMBER(O10),SUMIFS($O$6:$O$13,$A$6:$A$13,$A10)&lt;&gt;0),O10/SUMIFS($O$6:$O$13,$A$6:$A$13,$A10),"")</f>
         <v/>
       </c>
-      <c r="Q10" s="63" t="inlineStr">
+      <c r="Q10" s="61" t="inlineStr">
         <is>
           <t>won</t>
         </is>
       </c>
-      <c r="R10" s="64">
+      <c r="R10" s="62">
         <f>IF(AND(ISNUMBER(G10),ISNUMBER(O10),O10&lt;&gt;0),G10/O10,"")</f>
         <v/>
       </c>
-      <c r="S10" s="64">
+      <c r="S10" s="62">
         <f>IF(AND(ISNUMBER(N10),ISNUMBER(O10),O10&lt;&gt;0),N10/O10,"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="n">
+      <c r="A11" s="49" t="n">
         <v>2022</v>
       </c>
-      <c r="B11" s="51" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="C11" s="65" t="inlineStr">
+      <c r="C11" s="63" t="inlineStr">
         <is>
           <t>2022 post-census remap (Lehigh, Northampton, Carbon, part of Monroe)</t>
         </is>
       </c>
-      <c r="D11" s="51" t="inlineStr">
+      <c r="D11" s="49" t="inlineStr">
         <is>
           <t>Lisa Scheller</t>
         </is>
       </c>
-      <c r="E11" s="66" t="inlineStr">
+      <c r="E11" s="64" t="inlineStr">
         <is>
           <t>REP</t>
         </is>
@@ -17763,47 +17319,47 @@
         <f>IF(ISNUMBER(G11),G11+L11+SUMIFS($M$6:$M$13,$A$6:$A$13,$A11,$E$6:$E$13,"&lt;&gt;"&amp;$E11),"")</f>
         <v/>
       </c>
-      <c r="O11" s="49" t="n">
+      <c r="O11" s="47" t="n">
         <v>145527</v>
       </c>
-      <c r="P11" s="67">
+      <c r="P11" s="65">
         <f>IF(AND(ISNUMBER(O11),SUMIFS($O$6:$O$13,$A$6:$A$13,$A11)&lt;&gt;0),O11/SUMIFS($O$6:$O$13,$A$6:$A$13,$A11),"")</f>
         <v/>
       </c>
-      <c r="Q11" s="68" t="inlineStr">
+      <c r="Q11" s="66" t="inlineStr">
         <is>
           <t>lost</t>
         </is>
       </c>
-      <c r="R11" s="69">
+      <c r="R11" s="67">
         <f>IF(AND(ISNUMBER(G11),ISNUMBER(O11),O11&lt;&gt;0),G11/O11,"")</f>
         <v/>
       </c>
-      <c r="S11" s="69">
+      <c r="S11" s="67">
         <f>IF(AND(ISNUMBER(N11),ISNUMBER(O11),O11&lt;&gt;0),N11/O11,"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="n">
+      <c r="A12" s="49" t="n">
         <v>2024</v>
       </c>
-      <c r="B12" s="51" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="C12" s="65" t="inlineStr">
+      <c r="C12" s="63" t="inlineStr">
         <is>
           <t>2022 post-census remap (Lehigh, Northampton, Carbon, part of Monroe)</t>
         </is>
       </c>
-      <c r="D12" s="51" t="inlineStr">
+      <c r="D12" s="49" t="inlineStr">
         <is>
           <t>Susan Wild</t>
         </is>
       </c>
-      <c r="E12" s="70" t="inlineStr">
+      <c r="E12" s="68" t="inlineStr">
         <is>
           <t>DEM</t>
         </is>
@@ -17838,104 +17394,104 @@
         <f>IF(ISNUMBER(G12),G12+L12+SUMIFS($M$6:$M$13,$A$6:$A$13,$A12,$E$6:$E$13,"&lt;&gt;"&amp;$E12),"")</f>
         <v/>
       </c>
-      <c r="O12" s="49" t="n">
+      <c r="O12" s="47" t="n">
         <v>199626</v>
       </c>
-      <c r="P12" s="67">
+      <c r="P12" s="65">
         <f>IF(AND(ISNUMBER(O12),SUMIFS($O$6:$O$13,$A$6:$A$13,$A12)&lt;&gt;0),O12/SUMIFS($O$6:$O$13,$A$6:$A$13,$A12),"")</f>
         <v/>
       </c>
-      <c r="Q12" s="68" t="inlineStr">
+      <c r="Q12" s="66" t="inlineStr">
         <is>
           <t>lost</t>
         </is>
       </c>
-      <c r="R12" s="69">
+      <c r="R12" s="67">
         <f>IF(AND(ISNUMBER(G12),ISNUMBER(O12),O12&lt;&gt;0),G12/O12,"")</f>
         <v/>
       </c>
-      <c r="S12" s="69">
+      <c r="S12" s="67">
         <f>IF(AND(ISNUMBER(N12),ISNUMBER(O12),O12&lt;&gt;0),N12/O12,"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="55" t="n">
+      <c r="A13" s="53" t="n">
         <v>2024</v>
       </c>
-      <c r="B13" s="55" t="inlineStr">
+      <c r="B13" s="53" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="C13" s="56" t="inlineStr">
+      <c r="C13" s="54" t="inlineStr">
         <is>
           <t>2022 post-census remap (Lehigh, Northampton, Carbon, part of Monroe)</t>
         </is>
       </c>
-      <c r="D13" s="55" t="inlineStr">
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>Ryan Mackenzie</t>
         </is>
       </c>
-      <c r="E13" s="71" t="inlineStr">
+      <c r="E13" s="69" t="inlineStr">
         <is>
           <t>REP</t>
         </is>
       </c>
-      <c r="F13" s="58" t="inlineStr">
+      <c r="F13" s="56" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="G13" s="59" t="n">
+      <c r="G13" s="57" t="n">
         <v>1818407.11</v>
       </c>
-      <c r="H13" s="59" t="n">
+      <c r="H13" s="57" t="n">
         <v>1715167.2</v>
       </c>
-      <c r="I13" s="59" t="n">
+      <c r="I13" s="57" t="n">
         <v>103239.91</v>
       </c>
-      <c r="J13" s="59" t="n">
+      <c r="J13" s="57" t="n">
         <v>886645.14</v>
       </c>
-      <c r="K13" s="59" t="n">
+      <c r="K13" s="57" t="n">
         <v>419249.05</v>
       </c>
-      <c r="L13" s="59" t="n">
+      <c r="L13" s="57" t="n">
         <v>1333061.79</v>
       </c>
-      <c r="M13" s="59" t="n">
+      <c r="M13" s="57" t="n">
         <v>9962854.130000001</v>
       </c>
-      <c r="N13" s="60">
+      <c r="N13" s="58">
         <f>IF(ISNUMBER(G13),G13+L13+SUMIFS($M$6:$M$13,$A$6:$A$13,$A13,$E$6:$E$13,"&lt;&gt;"&amp;$E13),"")</f>
         <v/>
       </c>
-      <c r="O13" s="61" t="n">
+      <c r="O13" s="59" t="n">
         <v>203688</v>
       </c>
-      <c r="P13" s="62">
+      <c r="P13" s="60">
         <f>IF(AND(ISNUMBER(O13),SUMIFS($O$6:$O$13,$A$6:$A$13,$A13)&lt;&gt;0),O13/SUMIFS($O$6:$O$13,$A$6:$A$13,$A13),"")</f>
         <v/>
       </c>
-      <c r="Q13" s="63" t="inlineStr">
+      <c r="Q13" s="61" t="inlineStr">
         <is>
           <t>won</t>
         </is>
       </c>
-      <c r="R13" s="64">
+      <c r="R13" s="62">
         <f>IF(AND(ISNUMBER(G13),ISNUMBER(O13),O13&lt;&gt;0),G13/O13,"")</f>
         <v/>
       </c>
-      <c r="S13" s="64">
+      <c r="S13" s="62">
         <f>IF(AND(ISNUMBER(N13),ISNUMBER(O13),O13&lt;&gt;0),N13/O13,"")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="45" t="inlineStr">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>TOTAL VOTES CAST, AND WHAT TWO-PARTY SHARE LEAVES OUT</t>
         </is>
@@ -17983,141 +17539,141 @@
       <c r="S16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="n">
+      <c r="A17" s="49" t="n">
         <v>2018</v>
       </c>
-      <c r="B17" s="52" t="n"/>
-      <c r="C17" s="52" t="n"/>
+      <c r="B17" s="50" t="n"/>
+      <c r="C17" s="50" t="n"/>
       <c r="D17" s="14" t="inlineStr">
         <is>
           <t>All candidates on the ballot</t>
         </is>
       </c>
-      <c r="E17" s="52" t="n"/>
-      <c r="F17" s="52" t="n"/>
-      <c r="G17" s="52" t="n"/>
-      <c r="H17" s="52" t="n"/>
-      <c r="I17" s="52" t="n"/>
-      <c r="J17" s="52" t="n"/>
-      <c r="K17" s="52" t="n"/>
-      <c r="L17" s="52" t="n"/>
-      <c r="M17" s="52" t="n"/>
-      <c r="N17" s="52" t="n"/>
-      <c r="O17" s="49" t="n">
+      <c r="E17" s="50" t="n"/>
+      <c r="F17" s="50" t="n"/>
+      <c r="G17" s="50" t="n"/>
+      <c r="H17" s="50" t="n"/>
+      <c r="I17" s="50" t="n"/>
+      <c r="J17" s="50" t="n"/>
+      <c r="K17" s="50" t="n"/>
+      <c r="L17" s="50" t="n"/>
+      <c r="M17" s="50" t="n"/>
+      <c r="N17" s="50" t="n"/>
+      <c r="O17" s="47" t="n">
         <v>263360</v>
       </c>
-      <c r="P17" s="49" t="n">
+      <c r="P17" s="47" t="n">
         <v>8110</v>
       </c>
-      <c r="Q17" s="67">
+      <c r="Q17" s="65">
         <f>IF(AND(ISNUMBER(O17),ISNUMBER(P17),O17&lt;&gt;0),P17/O17,"")</f>
         <v/>
       </c>
-      <c r="R17" s="46">
+      <c r="R17" s="44">
         <f>IF(NOT(ISNUMBER(O17)),"not reported",IF(ABS(SUMIF($A$6:$A$13,$A17,$O$6:$O$13)+IF(ISNUMBER(P17),P17,0)-O17)&lt;0.5,"ok","MISMATCH"))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="51" t="n">
+      <c r="A18" s="49" t="n">
         <v>2020</v>
       </c>
-      <c r="B18" s="52" t="n"/>
-      <c r="C18" s="52" t="n"/>
+      <c r="B18" s="50" t="n"/>
+      <c r="C18" s="50" t="n"/>
       <c r="D18" s="14" t="inlineStr">
         <is>
           <t>All candidates on the ballot</t>
         </is>
       </c>
-      <c r="E18" s="52" t="n"/>
-      <c r="F18" s="52" t="n"/>
-      <c r="G18" s="52" t="n"/>
-      <c r="H18" s="52" t="n"/>
-      <c r="I18" s="52" t="n"/>
-      <c r="J18" s="52" t="n"/>
-      <c r="K18" s="52" t="n"/>
-      <c r="L18" s="52" t="n"/>
-      <c r="M18" s="52" t="n"/>
-      <c r="N18" s="52" t="n"/>
-      <c r="O18" s="49" t="n">
+      <c r="E18" s="50" t="n"/>
+      <c r="F18" s="50" t="n"/>
+      <c r="G18" s="50" t="n"/>
+      <c r="H18" s="50" t="n"/>
+      <c r="I18" s="50" t="n"/>
+      <c r="J18" s="50" t="n"/>
+      <c r="K18" s="50" t="n"/>
+      <c r="L18" s="50" t="n"/>
+      <c r="M18" s="50" t="n"/>
+      <c r="N18" s="50" t="n"/>
+      <c r="O18" s="47" t="n">
         <v>377404</v>
       </c>
-      <c r="P18" s="49" t="n">
+      <c r="P18" s="47" t="n">
         <v>522</v>
       </c>
-      <c r="Q18" s="67">
+      <c r="Q18" s="65">
         <f>IF(AND(ISNUMBER(O18),ISNUMBER(P18),O18&lt;&gt;0),P18/O18,"")</f>
         <v/>
       </c>
-      <c r="R18" s="46">
+      <c r="R18" s="44">
         <f>IF(NOT(ISNUMBER(O18)),"not reported",IF(ABS(SUMIF($A$6:$A$13,$A18,$O$6:$O$13)+IF(ISNUMBER(P18),P18,0)-O18)&lt;0.5,"ok","MISMATCH"))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="51" t="n">
+      <c r="A19" s="49" t="n">
         <v>2022</v>
       </c>
-      <c r="B19" s="52" t="n"/>
-      <c r="C19" s="52" t="n"/>
+      <c r="B19" s="50" t="n"/>
+      <c r="C19" s="50" t="n"/>
       <c r="D19" s="14" t="inlineStr">
         <is>
           <t>All candidates on the ballot</t>
         </is>
       </c>
-      <c r="E19" s="52" t="n"/>
-      <c r="F19" s="52" t="n"/>
-      <c r="G19" s="52" t="n"/>
-      <c r="H19" s="52" t="n"/>
-      <c r="I19" s="52" t="n"/>
-      <c r="J19" s="52" t="n"/>
-      <c r="K19" s="52" t="n"/>
-      <c r="L19" s="52" t="n"/>
-      <c r="M19" s="52" t="n"/>
-      <c r="N19" s="52" t="n"/>
-      <c r="O19" s="49" t="n">
+      <c r="E19" s="50" t="n"/>
+      <c r="F19" s="50" t="n"/>
+      <c r="G19" s="50" t="n"/>
+      <c r="H19" s="50" t="n"/>
+      <c r="I19" s="50" t="n"/>
+      <c r="J19" s="50" t="n"/>
+      <c r="K19" s="50" t="n"/>
+      <c r="L19" s="50" t="n"/>
+      <c r="M19" s="50" t="n"/>
+      <c r="N19" s="50" t="n"/>
+      <c r="O19" s="47" t="n">
         <v>297395</v>
       </c>
-      <c r="P19" s="49" t="n">
+      <c r="P19" s="47" t="n">
         <v>504</v>
       </c>
-      <c r="Q19" s="67">
+      <c r="Q19" s="65">
         <f>IF(AND(ISNUMBER(O19),ISNUMBER(P19),O19&lt;&gt;0),P19/O19,"")</f>
         <v/>
       </c>
-      <c r="R19" s="46">
+      <c r="R19" s="44">
         <f>IF(NOT(ISNUMBER(O19)),"not reported",IF(ABS(SUMIF($A$6:$A$13,$A19,$O$6:$O$13)+IF(ISNUMBER(P19),P19,0)-O19)&lt;0.5,"ok","MISMATCH"))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="n">
+      <c r="A20" s="49" t="n">
         <v>2024</v>
       </c>
-      <c r="B20" s="52" t="n"/>
-      <c r="C20" s="52" t="n"/>
+      <c r="B20" s="50" t="n"/>
+      <c r="C20" s="50" t="n"/>
       <c r="D20" s="14" t="inlineStr">
         <is>
           <t>All candidates on the ballot</t>
         </is>
       </c>
-      <c r="E20" s="52" t="n"/>
-      <c r="F20" s="52" t="n"/>
-      <c r="G20" s="52" t="n"/>
-      <c r="H20" s="52" t="n"/>
-      <c r="I20" s="52" t="n"/>
-      <c r="J20" s="52" t="n"/>
-      <c r="K20" s="52" t="n"/>
-      <c r="L20" s="52" t="n"/>
-      <c r="M20" s="52" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="O20" s="72" t="n"/>
-      <c r="P20" s="72" t="n"/>
-      <c r="Q20" s="73">
+      <c r="E20" s="50" t="n"/>
+      <c r="F20" s="50" t="n"/>
+      <c r="G20" s="50" t="n"/>
+      <c r="H20" s="50" t="n"/>
+      <c r="I20" s="50" t="n"/>
+      <c r="J20" s="50" t="n"/>
+      <c r="K20" s="50" t="n"/>
+      <c r="L20" s="50" t="n"/>
+      <c r="M20" s="50" t="n"/>
+      <c r="N20" s="50" t="n"/>
+      <c r="O20" s="70" t="n"/>
+      <c r="P20" s="70" t="n"/>
+      <c r="Q20" s="71">
         <f>IF(AND(ISNUMBER(O20),ISNUMBER(P20),O20&lt;&gt;0),P20/O20,"")</f>
         <v/>
       </c>
-      <c r="R20" s="46">
+      <c r="R20" s="44">
         <f>IF(NOT(ISNUMBER(O20)),"not reported",IF(ABS(SUMIF($A$6:$A$13,$A20,$O$6:$O$13)+IF(ISNUMBER(P20),P20,0)-O20)&lt;0.5,"ok","MISMATCH"))</f>
         <v/>
       </c>
@@ -18128,13 +17684,13 @@
           <t>Check: two-party plus third-party equals total, for every cycle that reports a total</t>
         </is>
       </c>
-      <c r="R21" s="74">
+      <c r="R21" s="72">
         <f>COUNTIF(R17:R20,"MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="45" t="inlineStr">
+      <c r="A23" s="43" t="inlineStr">
         <is>
           <t>HOW TO READ THIS SHEET</t>
         </is>

--- a/site/PA07_Campaign_Finance.xlsx
+++ b/site/PA07_Campaign_Finance.xlsx
@@ -3607,7 +3607,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T15:07:26Z</t>
+          <t>2026-09-28T23:32:20Z</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -4176,7 +4176,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Final full-cycle FEC totals and certified vote totals. One row per nominee per election. Retrieved 2026-09-17T15:59:59Z.</t>
+          <t>Final full-cycle FEC totals and certified vote totals. One row per nominee per election. Retrieved 2026-09-28T23:33:30Z.</t>
         </is>
       </c>
     </row>
@@ -6444,14 +6444,14 @@
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="85" t="inlineStr">
         <is>
-          <t>Current cycle: FEC / OpenFEC API, https://www.fec.gov/data/elections/house/PA/07/2026/, retrieved 2026-09-24T15:07:26Z</t>
+          <t>Current cycle: FEC / OpenFEC API, https://www.fec.gov/data/elections/house/PA/07/2026/, retrieved 2026-09-28T23:32:20Z</t>
         </is>
       </c>
     </row>
     <row r="5" ht="108" customHeight="1">
       <c r="A5" s="85" t="inlineStr">
         <is>
-          <t>History, finance: OpenFEC API (finance); certified results from sources/results.json, retrieved 2026-09-17T15:59:59Z</t>
+          <t>History, finance: OpenFEC API (finance); certified results from sources/results.json, retrieved 2026-09-28T23:33:30Z</t>
         </is>
       </c>
     </row>
@@ -29499,7 +29499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cycle-to-date from each committee's latest periodic FEC report. Coverage through 2026-06-30. Retrieved 2026-09-24T15:07:26Z.</t>
+          <t>Cycle-to-date from each committee's latest periodic FEC report. Coverage through 2026-06-30. Retrieved 2026-09-28T23:32:20Z.</t>
         </is>
       </c>
     </row>
@@ -31158,7 +31158,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Itemized disbursements (each over $200), 2026 cycle, through 2026-06-30. Categories assigned from the description on each report. Retrieved 2026-09-18T01:21:30Z.</t>
+          <t>Itemized disbursements (each over $200), 2026 cycle, through 2026-06-30. Categories assigned from the description on each report. Retrieved 2026-09-28T23:33:24Z.</t>
         </is>
       </c>
     </row>
@@ -32950,7 +32950,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Itemized individual contributions (each over $200), 2026 cycle, through 2026-06-30. FEC aggregates. Retrieved 2026-09-18T01:21:30Z.</t>
+          <t>Itemized individual contributions (each over $200), 2026 cycle, through 2026-06-30. FEC aggregates. Retrieved 2026-09-28T23:33:24Z.</t>
         </is>
       </c>
     </row>

--- a/site/PA07_Campaign_Finance.xlsx
+++ b/site/PA07_Campaign_Finance.xlsx
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-09T17:05:35Z</t>
+          <t>2026-10-15T11:59:42Z</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -6444,7 +6444,7 @@
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="85" t="inlineStr">
         <is>
-          <t>Current cycle: FEC / OpenFEC API, https://www.fec.gov/data/elections/house/PA/07/2026/, retrieved 2026-10-09T17:05:35Z</t>
+          <t>Current cycle: FEC / OpenFEC API, https://www.fec.gov/data/elections/house/PA/07/2026/, retrieved 2026-10-15T11:59:42Z</t>
         </is>
       </c>
     </row>
@@ -14900,7 +14900,7 @@
       </c>
       <c r="M168" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="M169" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="M170" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15023,7 +15023,7 @@
       </c>
       <c r="M171" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M172" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="M173" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="M174" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="M175" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="M176" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="M177" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="M178" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15351,7 +15351,7 @@
       </c>
       <c r="M179" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="M180" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
       </c>
       <c r="M181" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="M182" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="M183" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="M184" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="M185" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="M186" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15727,7 +15727,7 @@
       </c>
       <c r="M187" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15780,7 @@
       </c>
       <c r="M188" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15833,7 +15833,7 @@
       </c>
       <c r="M189" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15886,7 +15886,7 @@
       </c>
       <c r="M190" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="M191" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="M192" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16045,7 +16045,7 @@
       </c>
       <c r="M193" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="M194" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="M195" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16204,7 +16204,7 @@
       </c>
       <c r="M196" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16257,7 +16257,7 @@
       </c>
       <c r="M197" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="M198" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16351,7 +16351,7 @@
       </c>
       <c r="M199" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="M200" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16433,7 +16433,7 @@
       </c>
       <c r="M201" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="M202" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="M203" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="M204" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="M205" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16638,7 +16638,7 @@
       </c>
       <c r="M206" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16679,7 +16679,7 @@
       </c>
       <c r="M207" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="M208" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16761,7 +16761,7 @@
       </c>
       <c r="M209" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="M210" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16843,7 +16843,7 @@
       </c>
       <c r="M211" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M212" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16925,7 +16925,7 @@
       </c>
       <c r="M213" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -16966,7 +16966,7 @@
       </c>
       <c r="M214" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="M215" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="M216" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="M217" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="M218" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M219" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17212,7 +17212,7 @@
       </c>
       <c r="M220" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17253,7 +17253,7 @@
       </c>
       <c r="M221" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="M222" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17335,7 +17335,7 @@
       </c>
       <c r="M223" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17376,7 +17376,7 @@
       </c>
       <c r="M224" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="M225" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="M226" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17499,7 +17499,7 @@
       </c>
       <c r="M227" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="M228" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17581,7 +17581,7 @@
       </c>
       <c r="M229" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="M230" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17663,7 +17663,7 @@
       </c>
       <c r="M231" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17704,7 +17704,7 @@
       </c>
       <c r="M232" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17745,7 +17745,7 @@
       </c>
       <c r="M233" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17786,7 +17786,7 @@
       </c>
       <c r="M234" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17827,7 +17827,7 @@
       </c>
       <c r="M235" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="M236" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="M237" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17950,7 +17950,7 @@
       </c>
       <c r="M238" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17991,7 +17991,7 @@
       </c>
       <c r="M239" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="M240" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="M241" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="M242" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18155,7 +18155,7 @@
       </c>
       <c r="M243" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="M244" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="M245" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="M246" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M247" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="M248" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18401,7 +18401,7 @@
       </c>
       <c r="M249" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="M250" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="M251" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18524,7 +18524,7 @@
       </c>
       <c r="M252" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18565,7 +18565,7 @@
       </c>
       <c r="M253" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="M254" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="M255" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18688,7 +18688,7 @@
       </c>
       <c r="M256" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="M257" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18770,7 +18770,7 @@
       </c>
       <c r="M258" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="M259" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="M260" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="M261" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="M262" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -18973,7 +18973,7 @@
       <c r="L263" s="34" t="n"/>
       <c r="M263" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19014,7 +19014,7 @@
       </c>
       <c r="M264" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19055,7 +19055,7 @@
       </c>
       <c r="M265" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19096,7 +19096,7 @@
       </c>
       <c r="M266" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="M267" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19180,7 +19180,7 @@
       <c r="L268" s="34" t="n"/>
       <c r="M268" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19221,7 +19221,7 @@
       </c>
       <c r="M269" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19262,7 +19262,7 @@
       </c>
       <c r="M270" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19303,7 +19303,7 @@
       </c>
       <c r="M271" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19344,7 +19344,7 @@
       </c>
       <c r="M272" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="M273" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="M274" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="M275" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="M276" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="M277" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19590,7 +19590,7 @@
       </c>
       <c r="M278" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="M279" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19672,7 +19672,7 @@
       </c>
       <c r="M280" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="M281" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M282" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19795,7 +19795,7 @@
       </c>
       <c r="M283" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="M284" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="M285" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19918,7 +19918,7 @@
       </c>
       <c r="M286" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="M287" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="M288" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20041,7 +20041,7 @@
       </c>
       <c r="M289" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="M290" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20123,7 +20123,7 @@
       </c>
       <c r="M291" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20164,7 +20164,7 @@
       </c>
       <c r="M292" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="M293" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="M294" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="M295" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="M296" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20369,7 +20369,7 @@
       </c>
       <c r="M297" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="M298" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="M299" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20492,7 +20492,7 @@
       </c>
       <c r="M300" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20533,7 +20533,7 @@
       </c>
       <c r="M301" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20574,7 +20574,7 @@
       </c>
       <c r="M302" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="M303" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="M304" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="M305" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20738,7 +20738,7 @@
       </c>
       <c r="M306" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20791,7 +20791,7 @@
       </c>
       <c r="M307" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="M308" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="M309" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -20950,7 +20950,7 @@
       </c>
       <c r="M310" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21003,7 +21003,7 @@
       </c>
       <c r="M311" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21056,7 +21056,7 @@
       </c>
       <c r="M312" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="M313" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="M314" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21215,7 +21215,7 @@
       </c>
       <c r="M315" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21268,7 +21268,7 @@
       </c>
       <c r="M316" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21321,7 +21321,7 @@
       </c>
       <c r="M317" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M318" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21427,7 +21427,7 @@
       </c>
       <c r="M319" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21480,7 +21480,7 @@
       </c>
       <c r="M320" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="M321" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M322" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21615,7 +21615,7 @@
       </c>
       <c r="M323" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21656,7 +21656,7 @@
       </c>
       <c r="M324" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21697,7 +21697,7 @@
       </c>
       <c r="M325" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21738,7 +21738,7 @@
       </c>
       <c r="M326" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21779,7 +21779,7 @@
       </c>
       <c r="M327" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="M328" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21861,7 +21861,7 @@
       </c>
       <c r="M329" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21902,7 +21902,7 @@
       </c>
       <c r="M330" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21943,7 +21943,7 @@
       </c>
       <c r="M331" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="M332" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22025,7 +22025,7 @@
       </c>
       <c r="M333" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="M334" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="M335" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="M336" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22189,7 +22189,7 @@
       </c>
       <c r="M337" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22230,7 +22230,7 @@
       </c>
       <c r="M338" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22271,7 +22271,7 @@
       </c>
       <c r="M339" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22312,7 +22312,7 @@
       </c>
       <c r="M340" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22353,7 +22353,7 @@
       </c>
       <c r="M341" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22394,7 +22394,7 @@
       </c>
       <c r="M342" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="M343" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22476,7 +22476,7 @@
       </c>
       <c r="M344" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="M345" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22558,7 +22558,7 @@
       </c>
       <c r="M346" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22599,7 +22599,7 @@
       </c>
       <c r="M347" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22640,7 @@
       </c>
       <c r="M348" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22681,7 +22681,7 @@
       </c>
       <c r="M349" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22722,7 +22722,7 @@
       </c>
       <c r="M350" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22763,7 +22763,7 @@
       </c>
       <c r="M351" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M352" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22845,7 +22845,7 @@
       </c>
       <c r="M353" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="M354" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22927,7 +22927,7 @@
       </c>
       <c r="M355" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -22968,7 +22968,7 @@
       </c>
       <c r="M356" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23009,7 +23009,7 @@
       </c>
       <c r="M357" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23050,7 +23050,7 @@
       </c>
       <c r="M358" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23091,7 +23091,7 @@
       </c>
       <c r="M359" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23132,7 +23132,7 @@
       </c>
       <c r="M360" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23173,7 +23173,7 @@
       </c>
       <c r="M361" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23214,7 +23214,7 @@
       </c>
       <c r="M362" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23255,7 +23255,7 @@
       </c>
       <c r="M363" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23296,7 +23296,7 @@
       </c>
       <c r="M364" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23337,7 +23337,7 @@
       </c>
       <c r="M365" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23378,7 +23378,7 @@
       </c>
       <c r="M366" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
       </c>
       <c r="M367" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23460,7 +23460,7 @@
       </c>
       <c r="M368" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23501,7 +23501,7 @@
       </c>
       <c r="M369" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="M370" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="M371" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23624,7 +23624,7 @@
       </c>
       <c r="M372" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23665,7 +23665,7 @@
       </c>
       <c r="M373" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23706,7 +23706,7 @@
       </c>
       <c r="M374" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23747,7 +23747,7 @@
       </c>
       <c r="M375" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23788,7 +23788,7 @@
       </c>
       <c r="M376" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23829,7 +23829,7 @@
       </c>
       <c r="M377" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23870,7 +23870,7 @@
       </c>
       <c r="M378" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23911,7 +23911,7 @@
       </c>
       <c r="M379" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23952,7 +23952,7 @@
       </c>
       <c r="M380" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23993,7 +23993,7 @@
       </c>
       <c r="M381" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24034,7 +24034,7 @@
       </c>
       <c r="M382" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24075,7 +24075,7 @@
       </c>
       <c r="M383" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24116,7 +24116,7 @@
       </c>
       <c r="M384" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24157,7 +24157,7 @@
       </c>
       <c r="M385" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="M386" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24239,7 +24239,7 @@
       </c>
       <c r="M387" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24280,7 +24280,7 @@
       </c>
       <c r="M388" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24321,7 +24321,7 @@
       </c>
       <c r="M389" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24362,7 +24362,7 @@
       </c>
       <c r="M390" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24403,7 +24403,7 @@
       </c>
       <c r="M391" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M392" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24485,7 +24485,7 @@
       </c>
       <c r="M393" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24526,7 +24526,7 @@
       </c>
       <c r="M394" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24567,7 +24567,7 @@
       </c>
       <c r="M395" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24608,7 +24608,7 @@
       </c>
       <c r="M396" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="M397" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24690,7 +24690,7 @@
       </c>
       <c r="M398" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="M399" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24772,7 +24772,7 @@
       </c>
       <c r="M400" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24811,7 +24811,7 @@
       <c r="L401" s="34" t="n"/>
       <c r="M401" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24852,7 +24852,7 @@
       </c>
       <c r="M402" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24893,7 +24893,7 @@
       </c>
       <c r="M403" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M404" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -24975,7 +24975,7 @@
       </c>
       <c r="M405" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25018,7 +25018,7 @@
       <c r="L406" s="34" t="n"/>
       <c r="M406" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25059,7 +25059,7 @@
       </c>
       <c r="M407" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25100,7 +25100,7 @@
       </c>
       <c r="M408" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="M409" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25182,7 +25182,7 @@
       </c>
       <c r="M410" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25223,7 +25223,7 @@
       </c>
       <c r="M411" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25264,7 +25264,7 @@
       </c>
       <c r="M412" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25305,7 +25305,7 @@
       </c>
       <c r="M413" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25346,7 +25346,7 @@
       </c>
       <c r="M414" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25387,7 +25387,7 @@
       </c>
       <c r="M415" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25428,7 +25428,7 @@
       </c>
       <c r="M416" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M417" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25510,7 +25510,7 @@
       </c>
       <c r="M418" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25551,7 +25551,7 @@
       </c>
       <c r="M419" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25592,7 +25592,7 @@
       </c>
       <c r="M420" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25633,7 +25633,7 @@
       </c>
       <c r="M421" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25674,7 +25674,7 @@
       </c>
       <c r="M422" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25715,7 +25715,7 @@
       </c>
       <c r="M423" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25756,7 +25756,7 @@
       </c>
       <c r="M424" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25797,7 +25797,7 @@
       </c>
       <c r="M425" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25838,7 +25838,7 @@
       </c>
       <c r="M426" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25879,7 +25879,7 @@
       </c>
       <c r="M427" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25920,7 +25920,7 @@
       </c>
       <c r="M428" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -25961,7 +25961,7 @@
       </c>
       <c r="M429" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -30096,7 +30096,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cycle-to-date from each committee's latest periodic FEC report. Coverage through 2026-06-30. Retrieved 2026-10-09T17:05:35Z.</t>
+          <t>Cycle-to-date from each committee's latest periodic FEC report. Coverage through 2026-09-30. Retrieved 2026-10-15T11:59:42Z.</t>
         </is>
       </c>
     </row>
@@ -31787,7 +31787,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Itemized disbursements (each over $200), 2026 cycle, through 2026-06-30. Categories assigned from the description on each report. Retrieved 2026-10-09T17:06:16Z.</t>
+          <t>Itemized disbursements (each over $200), 2026 cycle, through 2026-09-30. Categories assigned from the description on each report. Retrieved 2026-10-15T12:00:17Z.</t>
         </is>
       </c>
     </row>
@@ -33579,7 +33579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Itemized individual contributions (each over $200), 2026 cycle, through 2026-06-30. FEC aggregates. Retrieved 2026-10-09T17:06:16Z.</t>
+          <t>Itemized individual contributions (each over $200), 2026 cycle, through 2026-09-30. FEC aggregates. Retrieved 2026-10-15T12:00:17Z.</t>
         </is>
       </c>
     </row>

--- a/site/PA07_Campaign_Finance.xlsx
+++ b/site/PA07_Campaign_Finance.xlsx
@@ -3607,7 +3607,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-15T11:59:42Z</t>
+          <t>2026-10-16T14:14:36Z</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -6444,7 +6444,7 @@
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="85" t="inlineStr">
         <is>
-          <t>Current cycle: FEC / OpenFEC API, https://www.fec.gov/data/elections/house/PA/07/2026/, retrieved 2026-10-15T11:59:42Z</t>
+          <t>Current cycle: FEC / OpenFEC API, https://www.fec.gov/data/elections/house/PA/07/2026/, retrieved 2026-10-16T14:14:36Z</t>
         </is>
       </c>
     </row>
@@ -6838,12 +6838,12 @@
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="33" t="n">
-        <v>2392215.23</v>
+        <v>4991635.39</v>
       </c>
       <c r="L5" s="34" t="n"/>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="33" t="n">
-        <v>1373792.39</v>
+        <v>3705480.38</v>
       </c>
       <c r="L6" s="34" t="n"/>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -6916,12 +6916,12 @@
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="33" t="n">
-        <v>1018422.84</v>
+        <v>1286155.01</v>
       </c>
       <c r="L7" s="34" t="n"/>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       <c r="L8" s="34" t="n"/>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -6994,12 +6994,12 @@
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
       <c r="K9" s="33" t="n">
-        <v>1942165.53</v>
+        <v>3916290.29</v>
       </c>
       <c r="L9" s="34" t="n"/>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
       <c r="K10" s="33" t="n">
-        <v>1342778.75</v>
+        <v>2848797.27</v>
       </c>
       <c r="L10" s="34" t="n"/>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7072,12 +7072,12 @@
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="33" t="n">
-        <v>599386.78</v>
+        <v>1067493.02</v>
       </c>
       <c r="L11" s="34" t="n"/>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="33" t="n">
-        <v>403000.03</v>
+        <v>596250.03</v>
       </c>
       <c r="L12" s="34" t="n"/>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7150,12 +7150,12 @@
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="33" t="n">
-        <v>5000</v>
+        <v>6090.07</v>
       </c>
       <c r="L13" s="34" t="n"/>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7189,12 +7189,12 @@
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="33" t="n">
-        <v>26085</v>
+        <v>456989.33</v>
       </c>
       <c r="L14" s="34" t="n"/>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       <c r="L15" s="34" t="n"/>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7267,12 +7267,12 @@
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="33" t="n">
-        <v>4357405.11</v>
+        <v>5167022.85</v>
       </c>
       <c r="L16" s="34" t="n"/>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7306,12 +7306,12 @@
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="33" t="n">
-        <v>1521927.85</v>
+        <v>3094595.78</v>
       </c>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7345,12 +7345,12 @@
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
       <c r="K18" s="33" t="n">
-        <v>2938717.17</v>
+        <v>2175666.98</v>
       </c>
       <c r="L18" s="34" t="n"/>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7384,12 +7384,12 @@
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="33" t="n">
-        <v>22583.23</v>
+        <v>4184.82</v>
       </c>
       <c r="L19" s="34" t="n"/>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7423,12 +7423,12 @@
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
       <c r="K20" s="33" t="n">
-        <v>1493241.01</v>
+        <v>1840430.27</v>
       </c>
       <c r="L20" s="34" t="n"/>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7462,12 +7462,12 @@
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
       <c r="K21" s="33" t="n">
-        <v>939107.04</v>
+        <v>1191087.7</v>
       </c>
       <c r="L21" s="34" t="n"/>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7501,12 +7501,12 @@
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
       <c r="K22" s="33" t="n">
-        <v>554133.97</v>
+        <v>649342.5699999999</v>
       </c>
       <c r="L22" s="34" t="n"/>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7540,12 +7540,12 @@
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="33" t="n">
-        <v>1042912.78</v>
+        <v>1284212.78</v>
       </c>
       <c r="L23" s="34" t="n"/>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
       <c r="K24" s="33" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="L24" s="34" t="n"/>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7618,12 +7618,12 @@
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
       <c r="K25" s="33" t="n">
-        <v>1779199.14</v>
+        <v>1982987.65</v>
       </c>
       <c r="L25" s="34" t="n"/>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       <c r="L26" s="34" t="n"/>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -30096,7 +30096,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cycle-to-date from each committee's latest periodic FEC report. Coverage through 2026-09-30. Retrieved 2026-10-15T11:59:42Z.</t>
+          <t>Cycle-to-date from each committee's latest periodic FEC report. Coverage through 2026-09-30. Retrieved 2026-10-16T14:14:36Z.</t>
         </is>
       </c>
     </row>
@@ -30238,35 +30238,35 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G6" s="44" t="n">
-        <v>4357405.11</v>
+        <v>5167022.85</v>
       </c>
       <c r="H6" s="44" t="n">
-        <v>1521927.85</v>
+        <v>3094595.78</v>
       </c>
       <c r="I6" s="44" t="n">
-        <v>2938717.17</v>
+        <v>2175666.98</v>
       </c>
       <c r="J6" s="44" t="n">
-        <v>22583.23</v>
+        <v>4184.82</v>
       </c>
       <c r="K6" s="44" t="n">
-        <v>1493241.01</v>
+        <v>1840430.27</v>
       </c>
       <c r="L6" s="44" t="n">
-        <v>554133.97</v>
+        <v>649342.5699999999</v>
       </c>
       <c r="M6" s="44" t="n">
-        <v>1042912.78</v>
+        <v>1284212.78</v>
       </c>
       <c r="N6" s="44" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="O6" s="44" t="n">
-        <v>1779199.14</v>
+        <v>1982987.65</v>
       </c>
       <c r="P6" s="44" t="n">
         <v>0</v>
@@ -30304,35 +30304,35 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G7" s="44" t="n">
-        <v>2392215.23</v>
+        <v>4991635.39</v>
       </c>
       <c r="H7" s="44" t="n">
-        <v>1373792.39</v>
+        <v>3705480.38</v>
       </c>
       <c r="I7" s="44" t="n">
-        <v>1018422.84</v>
+        <v>1286155.01</v>
       </c>
       <c r="J7" s="44" t="n">
         <v>15000</v>
       </c>
       <c r="K7" s="44" t="n">
-        <v>1942165.53</v>
+        <v>3916290.29</v>
       </c>
       <c r="L7" s="44" t="n">
-        <v>599386.78</v>
+        <v>1067493.02</v>
       </c>
       <c r="M7" s="44" t="n">
-        <v>403000.03</v>
+        <v>596250.03</v>
       </c>
       <c r="N7" s="44" t="n">
-        <v>5000</v>
+        <v>6090.07</v>
       </c>
       <c r="O7" s="44" t="n">
-        <v>26085</v>
+        <v>456989.33</v>
       </c>
       <c r="P7" s="44" t="n">
         <v>3500</v>

--- a/site/PA07_Campaign_Finance.xlsx
+++ b/site/PA07_Campaign_Finance.xlsx
@@ -3607,7 +3607,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:36Z</t>
+          <t>2026-10-17T13:10:02Z</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -4176,7 +4176,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Final full-cycle FEC totals and certified vote totals. One row per nominee per election. Retrieved 2026-10-09T17:06:51Z.</t>
+          <t>Final full-cycle FEC totals and certified vote totals. One row per nominee per election. Retrieved 2026-10-17T13:10:08Z.</t>
         </is>
       </c>
     </row>
@@ -6444,14 +6444,14 @@
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="85" t="inlineStr">
         <is>
-          <t>Current cycle: FEC / OpenFEC API, https://www.fec.gov/data/elections/house/PA/07/2026/, retrieved 2026-10-16T14:14:36Z</t>
+          <t>Current cycle: FEC / OpenFEC API, https://www.fec.gov/data/elections/house/PA/07/2026/, retrieved 2026-10-17T13:10:02Z</t>
         </is>
       </c>
     </row>
     <row r="5" ht="108" customHeight="1">
       <c r="A5" s="85" t="inlineStr">
         <is>
-          <t>History, finance: OpenFEC API (finance); certified results from sources/results.json, retrieved 2026-10-09T17:06:51Z</t>
+          <t>History, finance: OpenFEC API (finance); certified results from sources/results.json, retrieved 2026-10-17T13:10:08Z</t>
         </is>
       </c>
     </row>
@@ -30096,7 +30096,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cycle-to-date from each committee's latest periodic FEC report. Coverage through 2026-09-30. Retrieved 2026-10-16T14:14:36Z.</t>
+          <t>Cycle-to-date from each committee's latest periodic FEC report. Coverage through 2026-09-30. Retrieved 2026-10-17T13:10:02Z.</t>
         </is>
       </c>
     </row>

--- a/site/PA07_Campaign_Finance.xlsx
+++ b/site/PA07_Campaign_Finance.xlsx
@@ -3607,7 +3607,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23T15:03:17Z</t>
+          <t>2026-10-24T13:15:11Z</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -4176,7 +4176,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Final full-cycle FEC totals and certified vote totals. One row per nominee per election. Retrieved 2026-10-17T13:10:08Z.</t>
+          <t>Final full-cycle FEC totals and certified vote totals. One row per nominee per election. Retrieved 2026-10-24T13:15:22Z.</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
         <v>1279735.82</v>
       </c>
       <c r="L10" s="59" t="n">
-        <v>654900.95</v>
+        <v>655273.84</v>
       </c>
       <c r="M10" s="59" t="n">
         <v>10853652.49</v>
@@ -6444,14 +6444,14 @@
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="85" t="inlineStr">
         <is>
-          <t>Current cycle: FEC / OpenFEC API, https://www.fec.gov/data/elections/house/PA/07/2026/, retrieved 2026-10-23T15:03:17Z</t>
+          <t>Current cycle: FEC / OpenFEC API, https://www.fec.gov/data/elections/house/PA/07/2026/, retrieved 2026-10-24T13:15:11Z</t>
         </is>
       </c>
     </row>
     <row r="5" ht="108" customHeight="1">
       <c r="A5" s="85" t="inlineStr">
         <is>
-          <t>History, finance: OpenFEC API (finance); certified results from sources/results.json, retrieved 2026-10-17T13:10:08Z</t>
+          <t>History, finance: OpenFEC API (finance); certified results from sources/results.json, retrieved 2026-10-24T13:15:22Z</t>
         </is>
       </c>
     </row>
@@ -29253,7 +29253,7 @@
       <c r="I502" s="5" t="n"/>
       <c r="J502" s="5" t="n"/>
       <c r="K502" s="33" t="n">
-        <v>654900.95</v>
+        <v>655273.84</v>
       </c>
       <c r="L502" s="34" t="n"/>
       <c r="M502" s="5" t="inlineStr">
@@ -31895,7 +31895,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cycle-to-date from each committee's latest periodic FEC report. Coverage through 2026-10-14. Retrieved 2026-10-23T15:03:17Z.</t>
+          <t>Cycle-to-date from each committee's latest periodic FEC report. Coverage through 2026-10-14. Retrieved 2026-10-24T13:15:11Z.</t>
         </is>
       </c>
     </row>
